--- a/Perfil_NEXUS_GERAL.xlsx
+++ b/Perfil_NEXUS_GERAL.xlsx
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ONPUTAIA</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -26141,7 +26141,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MUATHAPUE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -27308,7 +27308,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MUATHAPUE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -27886,7 +27886,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MATHUPE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -28153,7 +28153,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MUATHAPUE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -44151,7 +44151,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>MORRUPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -46230,7 +46230,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>MURRUPELENE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -87335,13 +87335,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3757C76B-B83A-46B8-AB23-E0A40B01E90E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EC3F0DE-78B7-4E11-8E2B-73DCDBD2DF04}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7C70CEB-AD08-479B-8449-AEE4591FB6F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8314A507-1774-4DA7-8EBA-1A9DB1764830}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B8D05DF-9BC2-4BC1-976D-DCA4247BDAF1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8018125-ACB8-47D2-ABB0-998D0CFEB7A3}"/>
 </file>
--- a/Perfil_NEXUS_GERAL.xlsx
+++ b/Perfil_NEXUS_GERAL.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BO449"/>
+  <dimension ref="A1:BO450"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -69409,7 +69409,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -69605,7 +69605,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -69798,7 +69798,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -70027,7 +70027,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -70241,7 +70241,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -70427,7 +70427,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -70611,7 +70611,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -70858,7 +70858,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -71049,7 +71049,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -71230,7 +71230,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -71436,7 +71436,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -71597,7 +71597,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -71826,7 +71826,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -72042,7 +72042,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -72264,7 +72264,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -72491,7 +72491,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -72715,7 +72715,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -72914,7 +72914,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -73158,7 +73158,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -73377,7 +73377,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -73601,7 +73601,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -73782,7 +73782,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -74032,7 +74032,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -74256,7 +74256,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -74450,7 +74450,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -74626,7 +74626,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -74842,7 +74842,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -75013,7 +75013,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -75192,7 +75192,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -77629,7 +77629,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>JOAO DAMASIO EDUARDO</t>
+          <t>ISELIA MIGUEL</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -77659,12 +77659,12 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>Cartão de Eleitor</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>020105937566Q</t>
+          <t>092216-26042359713(090774-01/480)</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
@@ -77674,14 +77674,14 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="L405">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="M405">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N405" t="inlineStr">
         <is>
@@ -77690,7 +77690,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>9a classe</t>
+          <t>7a classe</t>
         </is>
       </c>
       <c r="P405" t="inlineStr">
@@ -77699,36 +77699,11 @@
         </is>
       </c>
       <c r="Q405">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R405" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="S405" t="inlineStr">
-        <is>
-          <t>PORQUE ME CASEI COM OUTRA MULHER.</t>
-        </is>
-      </c>
-      <c r="T405" t="inlineStr">
-        <is>
-          <t>06/2019</t>
-        </is>
-      </c>
-      <c r="U405" t="inlineStr">
-        <is>
-          <t>MUEDA</t>
-        </is>
-      </c>
-      <c r="V405" t="inlineStr">
-        <is>
-          <t>Sozinha/o com seu AF da sua origem</t>
-        </is>
-      </c>
-      <c r="W405" t="inlineStr">
-        <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="X405" t="inlineStr">
@@ -77738,7 +77713,7 @@
       </c>
       <c r="Y405" t="inlineStr">
         <is>
-          <t>VENDA DE CARVAO</t>
+          <t>VENDA DE BOLINHOS FRITOS</t>
         </is>
       </c>
       <c r="Z405" t="inlineStr">
@@ -77763,7 +77738,7 @@
       </c>
       <c r="AF405" t="inlineStr">
         <is>
-          <t>RECEBI KIT DOMESTICOS (BALDE, PANELA )</t>
+          <t>MATERIAL DE USO CASEIRO</t>
         </is>
       </c>
       <c r="AG405">
@@ -77771,24 +77746,27 @@
       </c>
       <c r="AH405" t="inlineStr">
         <is>
+          <t>MATERIAL DE HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="AI405">
+        <v>2</v>
+      </c>
+      <c r="AJ405" t="inlineStr">
+        <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AJ405" t="inlineStr">
+      <c r="AL405" t="inlineStr">
         <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AL405" t="inlineStr">
+      <c r="AN405" t="inlineStr">
         <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AN405" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
       <c r="AP405" t="inlineStr">
         <is>
           <t>Não</t>
@@ -77801,21 +77779,31 @@
       </c>
       <c r="BB405" t="inlineStr">
         <is>
-          <t>860-866-873</t>
+          <t>868-598-265</t>
         </is>
       </c>
       <c r="BC405" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BD405" t="inlineStr">
-        <is>
-          <t>835-317-432</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BE405" t="inlineStr">
         <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BF405" t="inlineStr">
+        <is>
+          <t>Mãe/pai</t>
+        </is>
+      </c>
+      <c r="BG405" t="inlineStr">
+        <is>
+          <t>868-069-171</t>
+        </is>
+      </c>
+      <c r="BH405" t="inlineStr">
+        <is>
           <t>Não</t>
         </is>
       </c>
@@ -77826,17 +77814,22 @@
       </c>
       <c r="BL405" t="inlineStr">
         <is>
-          <t>Deslocado</t>
+          <t>VBG Interno</t>
         </is>
       </c>
       <c r="BM405" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>VBG Interno</t>
+        </is>
+      </c>
+      <c r="BN405" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="BO405" t="inlineStr">
         <is>
-          <t>PRJ_0482</t>
+          <t>PRJ_0588</t>
         </is>
       </c>
     </row>
@@ -77848,7 +77841,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>JOAO RAUL VINTAN</t>
+          <t>JOAO DAMASIO EDUARDO</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -77883,7 +77876,7 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>020106557905Q</t>
+          <t>020105937566Q</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
@@ -77897,34 +77890,47 @@
         </is>
       </c>
       <c r="L406">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="M406">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N406" t="inlineStr">
         <is>
-          <t>Solteria/o</t>
+          <t>Casada/o</t>
         </is>
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>Ensino primário</t>
+          <t>9a classe</t>
         </is>
       </c>
       <c r="P406" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q406">
+        <v>3</v>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>PORQUE ME CASEI COM OUTRA MULHER.</t>
         </is>
       </c>
       <c r="T406" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>06/2019</t>
         </is>
       </c>
       <c r="U406" t="inlineStr">
         <is>
-          <t>MUIDUMBE</t>
+          <t>MUEDA</t>
         </is>
       </c>
       <c r="V406" t="inlineStr">
@@ -77944,12 +77950,12 @@
       </c>
       <c r="Y406" t="inlineStr">
         <is>
-          <t>VENDA DE BOLINHOS</t>
+          <t>VENDA DE CARVAO</t>
         </is>
       </c>
       <c r="Z406" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="AA406" t="inlineStr">
@@ -77969,7 +77975,7 @@
       </c>
       <c r="AF406" t="inlineStr">
         <is>
-          <t>RECEBI PRODUTOS ALIMENTARES DA PMA</t>
+          <t>RECEBI KIT DOMESTICOS (BALDE, PANELA )</t>
         </is>
       </c>
       <c r="AG406">
@@ -78007,7 +78013,7 @@
       </c>
       <c r="BB406" t="inlineStr">
         <is>
-          <t>869-665-659</t>
+          <t>860-866-873</t>
         </is>
       </c>
       <c r="BC406" t="inlineStr">
@@ -78017,26 +78023,11 @@
       </c>
       <c r="BD406" t="inlineStr">
         <is>
-          <t>846-546-341</t>
+          <t>835-317-432</t>
         </is>
       </c>
       <c r="BE406" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BF406" t="inlineStr">
-        <is>
-          <t>Irmã/o</t>
-        </is>
-      </c>
-      <c r="BG406" t="inlineStr">
-        <is>
-          <t>868-574-445</t>
-        </is>
-      </c>
-      <c r="BH406" t="inlineStr">
-        <is>
           <t>Não</t>
         </is>
       </c>
@@ -78057,7 +78048,7 @@
       </c>
       <c r="BO406" t="inlineStr">
         <is>
-          <t>PRJ_0439</t>
+          <t>PRJ_0482</t>
         </is>
       </c>
     </row>
@@ -78069,7 +78060,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>JOAQUINA MATEUS LUIS</t>
+          <t>JOAO RAUL VINTAN</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -78104,7 +78095,7 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>020908894100N</t>
+          <t>020106557905Q</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
@@ -78114,14 +78105,14 @@
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="L407">
-        <v>2005</v>
+        <v>1994</v>
       </c>
       <c r="M407">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="N407" t="inlineStr">
         <is>
@@ -78130,7 +78121,7 @@
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t>11a classe</t>
+          <t>Ensino primário</t>
         </is>
       </c>
       <c r="P407" t="inlineStr">
@@ -78145,7 +78136,7 @@
       </c>
       <c r="U407" t="inlineStr">
         <is>
-          <t>MOC. DA PRAIA</t>
+          <t>MUIDUMBE</t>
         </is>
       </c>
       <c r="V407" t="inlineStr">
@@ -78155,12 +78146,17 @@
       </c>
       <c r="W407" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="X407" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Y407" t="inlineStr">
+        <is>
+          <t>VENDA DE BOLINHOS</t>
         </is>
       </c>
       <c r="Z407" t="inlineStr">
@@ -78185,7 +78181,7 @@
       </c>
       <c r="AF407" t="inlineStr">
         <is>
-          <t>PRODUTOS ALIMENTARES</t>
+          <t>RECEBI PRODUTOS ALIMENTARES DA PMA</t>
         </is>
       </c>
       <c r="AG407">
@@ -78218,7 +78214,22 @@
       </c>
       <c r="BA407" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BB407" t="inlineStr">
+        <is>
+          <t>869-665-659</t>
+        </is>
+      </c>
+      <c r="BC407" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BD407" t="inlineStr">
+        <is>
+          <t>846-546-341</t>
         </is>
       </c>
       <c r="BE407" t="inlineStr">
@@ -78233,7 +78244,7 @@
       </c>
       <c r="BG407" t="inlineStr">
         <is>
-          <t>873-883-337</t>
+          <t>868-574-445</t>
         </is>
       </c>
       <c r="BH407" t="inlineStr">
@@ -78243,7 +78254,7 @@
       </c>
       <c r="BK407" t="inlineStr">
         <is>
-          <t>Número alternativo</t>
+          <t>Número proprio</t>
         </is>
       </c>
       <c r="BL407" t="inlineStr">
@@ -78258,7 +78269,7 @@
       </c>
       <c r="BO407" t="inlineStr">
         <is>
-          <t>PRJ_0476</t>
+          <t>PRJ_0439</t>
         </is>
       </c>
     </row>
@@ -78270,7 +78281,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>JOSE RAIMUNDO DAMASSENO</t>
+          <t>JOAQUINA MATEUS LUIS</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -78305,7 +78316,7 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>021208881790Q</t>
+          <t>020908894100N</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
@@ -78315,14 +78326,14 @@
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="L408">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="M408">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N408" t="inlineStr">
         <is>
@@ -78331,7 +78342,7 @@
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t>10a classe</t>
+          <t>11a classe</t>
         </is>
       </c>
       <c r="P408" t="inlineStr">
@@ -78341,12 +78352,12 @@
       </c>
       <c r="T408" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="U408" t="inlineStr">
         <is>
-          <t>MUIDUMBE</t>
+          <t>MOC. DA PRAIA</t>
         </is>
       </c>
       <c r="V408" t="inlineStr">
@@ -78386,7 +78397,7 @@
       </c>
       <c r="AF408" t="inlineStr">
         <is>
-          <t>RECIPIENTE PARA CONSERVACAO DE AGUA</t>
+          <t>PRODUTOS ALIMENTARES</t>
         </is>
       </c>
       <c r="AG408">
@@ -78419,16 +78430,6 @@
       </c>
       <c r="BA408" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BB408" t="inlineStr">
-        <is>
-          <t>865-361-958</t>
-        </is>
-      </c>
-      <c r="BC408" t="inlineStr">
-        <is>
           <t>Não</t>
         </is>
       </c>
@@ -78439,12 +78440,12 @@
       </c>
       <c r="BF408" t="inlineStr">
         <is>
-          <t>Tio/a</t>
+          <t>Irmã/o</t>
         </is>
       </c>
       <c r="BG408" t="inlineStr">
         <is>
-          <t>878-647-623</t>
+          <t>873-883-337</t>
         </is>
       </c>
       <c r="BH408" t="inlineStr">
@@ -78454,7 +78455,7 @@
       </c>
       <c r="BK408" t="inlineStr">
         <is>
-          <t>Número proprio</t>
+          <t>Número alternativo</t>
         </is>
       </c>
       <c r="BL408" t="inlineStr">
@@ -78467,14 +78468,9 @@
           <t>IDP</t>
         </is>
       </c>
-      <c r="BN408" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
       <c r="BO408" t="inlineStr">
         <is>
-          <t>PRJ_0477</t>
+          <t>PRJ_0476</t>
         </is>
       </c>
     </row>
@@ -78486,7 +78482,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>JOSEFINA LIKATE ATIBO</t>
+          <t>JOSE RAIMUNDO DAMASSENO</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -78521,7 +78517,7 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>021208897317I</t>
+          <t>021208881790Q</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
@@ -78531,41 +78527,33 @@
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="L409">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="M409">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t>Casada/o</t>
+          <t>Solteria/o</t>
         </is>
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>9a classe</t>
+          <t>10a classe</t>
         </is>
       </c>
       <c r="P409" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q409">
-        <v>4</v>
-      </c>
-      <c r="R409" t="inlineStr">
-        <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T409" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="U409" t="inlineStr">
@@ -78575,12 +78563,12 @@
       </c>
       <c r="V409" t="inlineStr">
         <is>
-          <t>Familia acolhedora</t>
+          <t>Sozinha/o com seu AF da sua origem</t>
         </is>
       </c>
       <c r="W409" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="X409" t="inlineStr">
@@ -78610,7 +78598,7 @@
       </c>
       <c r="AF409" t="inlineStr">
         <is>
-          <t>RECEBI MATERIAL DE COZINHA DA VISAO MUNDIAL.</t>
+          <t>RECIPIENTE PARA CONSERVACAO DE AGUA</t>
         </is>
       </c>
       <c r="AG409">
@@ -78643,6 +78631,16 @@
       </c>
       <c r="BA409" t="inlineStr">
         <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BB409" t="inlineStr">
+        <is>
+          <t>865-361-958</t>
+        </is>
+      </c>
+      <c r="BC409" t="inlineStr">
+        <is>
           <t>Não</t>
         </is>
       </c>
@@ -78653,12 +78651,12 @@
       </c>
       <c r="BF409" t="inlineStr">
         <is>
-          <t>Esposo/a</t>
+          <t>Tio/a</t>
         </is>
       </c>
       <c r="BG409" t="inlineStr">
         <is>
-          <t>863-586-608</t>
+          <t>878-647-623</t>
         </is>
       </c>
       <c r="BH409" t="inlineStr">
@@ -78668,7 +78666,7 @@
       </c>
       <c r="BK409" t="inlineStr">
         <is>
-          <t>Número alternativo</t>
+          <t>Número proprio</t>
         </is>
       </c>
       <c r="BL409" t="inlineStr">
@@ -78681,9 +78679,14 @@
           <t>IDP</t>
         </is>
       </c>
+      <c r="BN409" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
       <c r="BO409" t="inlineStr">
         <is>
-          <t>PRJ_0429</t>
+          <t>PRJ_0477</t>
         </is>
       </c>
     </row>
@@ -78695,7 +78698,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>LINDA LOURENCO</t>
+          <t>JOSEFINA LIKATE ATIBO</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -78725,12 +78728,12 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Cartão de Eleitor</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>090436-27052331080(090793-06/123)</t>
+          <t>021208897317I</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
@@ -78744,10 +78747,10 @@
         </is>
       </c>
       <c r="L410">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="M410">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N410" t="inlineStr">
         <is>
@@ -78756,7 +78759,7 @@
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>7a classe</t>
+          <t>9a classe</t>
         </is>
       </c>
       <c r="P410" t="inlineStr">
@@ -78772,6 +78775,26 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>11/2020</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>MUIDUMBE</t>
+        </is>
+      </c>
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>Familia acolhedora</t>
+        </is>
+      </c>
+      <c r="W410" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="X410" t="inlineStr">
         <is>
           <t>Não</t>
@@ -78794,7 +78817,35 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AF410" t="inlineStr">
+        <is>
+          <t>RECEBI MATERIAL DE COZINHA DA VISAO MUNDIAL.</t>
+        </is>
+      </c>
+      <c r="AG410">
+        <v>1</v>
+      </c>
+      <c r="AH410" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AJ410" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AL410" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AN410" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="AP410" t="inlineStr">
@@ -78804,16 +78855,6 @@
       </c>
       <c r="BA410" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BB410" t="inlineStr">
-        <is>
-          <t>873-371-198</t>
-        </is>
-      </c>
-      <c r="BC410" t="inlineStr">
-        <is>
           <t>Não</t>
         </is>
       </c>
@@ -78829,7 +78870,7 @@
       </c>
       <c r="BG410" t="inlineStr">
         <is>
-          <t>861-993-042</t>
+          <t>863-586-608</t>
         </is>
       </c>
       <c r="BH410" t="inlineStr">
@@ -78839,27 +78880,22 @@
       </c>
       <c r="BK410" t="inlineStr">
         <is>
-          <t>Número proprio</t>
+          <t>Número alternativo</t>
         </is>
       </c>
       <c r="BL410" t="inlineStr">
         <is>
-          <t>VBG Interno</t>
+          <t>Deslocado</t>
         </is>
       </c>
       <c r="BM410" t="inlineStr">
         <is>
-          <t>VBG Interno</t>
-        </is>
-      </c>
-      <c r="BN410" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="BO410" t="inlineStr">
         <is>
-          <t>PRJ_0581</t>
+          <t>PRJ_0429</t>
         </is>
       </c>
     </row>
@@ -78871,7 +78907,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>MALINDA JOSE CHITUNGULO MADIDINE</t>
+          <t>LINDA LOURENCO</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -78901,12 +78937,12 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>Cartão de Eleitor</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>031304089251F</t>
+          <t>090436-27052331080(090793-06/123)</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
@@ -78920,10 +78956,10 @@
         </is>
       </c>
       <c r="L411">
-        <v>1999</v>
+        <v>1995</v>
       </c>
       <c r="M411">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N411" t="inlineStr">
         <is>
@@ -78932,7 +78968,7 @@
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>10a classe</t>
+          <t>7a classe</t>
         </is>
       </c>
       <c r="P411" t="inlineStr">
@@ -78941,33 +78977,13 @@
         </is>
       </c>
       <c r="Q411">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R411" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="T411" t="inlineStr">
-        <is>
-          <t>6/2022</t>
-        </is>
-      </c>
-      <c r="U411" t="inlineStr">
-        <is>
-          <t>MOCIMBOA DA PRAIA</t>
-        </is>
-      </c>
-      <c r="V411" t="inlineStr">
-        <is>
-          <t>Familia acolhedora</t>
-        </is>
-      </c>
-      <c r="W411" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="X411" t="inlineStr">
         <is>
           <t>Não</t>
@@ -78990,68 +79006,12 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AF411" t="inlineStr">
-        <is>
-          <t>PRODUTOS ALIMENTARES</t>
-        </is>
-      </c>
-      <c r="AG411">
-        <v>1</v>
-      </c>
-      <c r="AH411" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AJ411" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AL411" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AN411" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AP411" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AQ411" t="inlineStr">
-        <is>
-          <t>MATERIA-PRIMA PARA NEGOCIO (TRIGO, OLEO)</t>
-        </is>
-      </c>
-      <c r="AR411">
-        <v>1</v>
-      </c>
-      <c r="AS411" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AU411" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AW411" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AY411" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BA411" t="inlineStr">
@@ -79061,7 +79021,7 @@
       </c>
       <c r="BB411" t="inlineStr">
         <is>
-          <t>860-460-571</t>
+          <t>873-371-198</t>
         </is>
       </c>
       <c r="BC411" t="inlineStr">
@@ -79076,12 +79036,12 @@
       </c>
       <c r="BF411" t="inlineStr">
         <is>
-          <t>Avô/avó</t>
+          <t>Esposo/a</t>
         </is>
       </c>
       <c r="BG411" t="inlineStr">
         <is>
-          <t>867-867-309</t>
+          <t>861-993-042</t>
         </is>
       </c>
       <c r="BH411" t="inlineStr">
@@ -79096,17 +79056,22 @@
       </c>
       <c r="BL411" t="inlineStr">
         <is>
-          <t>Deslocado</t>
+          <t>VBG Interno</t>
         </is>
       </c>
       <c r="BM411" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>VBG Interno</t>
+        </is>
+      </c>
+      <c r="BN411" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="BO411" t="inlineStr">
         <is>
-          <t>PRJ_0474</t>
+          <t>PRJ_0581</t>
         </is>
       </c>
     </row>
@@ -79118,7 +79083,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>NADIA EDUARDO JAIME</t>
+          <t>MALINDA JOSE CHITUNGULO MADIDINE</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -79153,7 +79118,7 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>031308886953B</t>
+          <t>031304089251F</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
@@ -79167,10 +79132,10 @@
         </is>
       </c>
       <c r="L412">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="M412">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="N412" t="inlineStr">
         <is>
@@ -79179,7 +79144,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t>11a classe</t>
+          <t>10a classe</t>
         </is>
       </c>
       <c r="P412" t="inlineStr">
@@ -79188,13 +79153,33 @@
         </is>
       </c>
       <c r="Q412">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R412" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>6/2022</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>MOCIMBOA DA PRAIA</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>Familia acolhedora</t>
+        </is>
+      </c>
+      <c r="W412" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="X412" t="inlineStr">
         <is>
           <t>Não</t>
@@ -79222,7 +79207,7 @@
       </c>
       <c r="AF412" t="inlineStr">
         <is>
-          <t>MATERIAL DE HIGIENE</t>
+          <t>PRODUTOS ALIMENTARES</t>
         </is>
       </c>
       <c r="AG412">
@@ -79230,11 +79215,8 @@
       </c>
       <c r="AH412" t="inlineStr">
         <is>
-          <t>MATERIAL DE USO CASEIRO</t>
-        </is>
-      </c>
-      <c r="AI412">
-        <v>2</v>
+          <t>##N/A##</t>
+        </is>
       </c>
       <c r="AJ412" t="inlineStr">
         <is>
@@ -79253,7 +79235,35 @@
       </c>
       <c r="AP412" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AQ412" t="inlineStr">
+        <is>
+          <t>MATERIA-PRIMA PARA NEGOCIO (TRIGO, OLEO)</t>
+        </is>
+      </c>
+      <c r="AR412">
+        <v>1</v>
+      </c>
+      <c r="AS412" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AU412" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AW412" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AY412" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="BA412" t="inlineStr">
@@ -79263,17 +79273,12 @@
       </c>
       <c r="BB412" t="inlineStr">
         <is>
-          <t>862-621-815</t>
+          <t>860-460-571</t>
         </is>
       </c>
       <c r="BC412" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BD412" t="inlineStr">
-        <is>
-          <t>879-221-910</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BE412" t="inlineStr">
@@ -79283,12 +79288,12 @@
       </c>
       <c r="BF412" t="inlineStr">
         <is>
-          <t>Mãe/pai</t>
+          <t>Avô/avó</t>
         </is>
       </c>
       <c r="BG412" t="inlineStr">
         <is>
-          <t>871-889-118</t>
+          <t>867-867-309</t>
         </is>
       </c>
       <c r="BH412" t="inlineStr">
@@ -79303,22 +79308,17 @@
       </c>
       <c r="BL412" t="inlineStr">
         <is>
-          <t>VBG Interno</t>
+          <t>Deslocado</t>
         </is>
       </c>
       <c r="BM412" t="inlineStr">
         <is>
-          <t>VBG Interno</t>
-        </is>
-      </c>
-      <c r="BN412" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="BO412" t="inlineStr">
         <is>
-          <t>PRJ_0579</t>
+          <t>PRJ_0474</t>
         </is>
       </c>
     </row>
@@ -79330,7 +79330,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>RAFAEL SALIMO REBOTE</t>
+          <t>NADIA EDUARDO JAIME</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -79365,7 +79365,7 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>030908884084A</t>
+          <t>031308886953B</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
@@ -79375,46 +79375,34 @@
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="L413">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="M413">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t>Solteria/o</t>
+          <t>Casada/o</t>
         </is>
       </c>
       <c r="O413" t="inlineStr">
         <is>
-          <t>10a classe</t>
+          <t>11a classe</t>
         </is>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="T413" t="inlineStr">
-        <is>
-          <t>03/2025</t>
-        </is>
-      </c>
-      <c r="U413" t="inlineStr">
-        <is>
-          <t>MEMBA</t>
-        </is>
-      </c>
-      <c r="V413" t="inlineStr">
-        <is>
-          <t>Familia acolhedora</t>
-        </is>
-      </c>
-      <c r="W413" t="inlineStr">
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q413">
+        <v>2</v>
+      </c>
+      <c r="R413" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -79441,7 +79429,38 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AF413" t="inlineStr">
+        <is>
+          <t>MATERIAL DE HIGIENE</t>
+        </is>
+      </c>
+      <c r="AG413">
+        <v>1</v>
+      </c>
+      <c r="AH413" t="inlineStr">
+        <is>
+          <t>MATERIAL DE USO CASEIRO</t>
+        </is>
+      </c>
+      <c r="AI413">
+        <v>2</v>
+      </c>
+      <c r="AJ413" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AL413" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AN413" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="AP413" t="inlineStr">
@@ -79456,12 +79475,17 @@
       </c>
       <c r="BB413" t="inlineStr">
         <is>
-          <t>877-297-168</t>
+          <t>862-621-815</t>
         </is>
       </c>
       <c r="BC413" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BD413" t="inlineStr">
+        <is>
+          <t>879-221-910</t>
         </is>
       </c>
       <c r="BE413" t="inlineStr">
@@ -79471,27 +79495,17 @@
       </c>
       <c r="BF413" t="inlineStr">
         <is>
-          <t>Tio/a</t>
+          <t>Mãe/pai</t>
         </is>
       </c>
       <c r="BG413" t="inlineStr">
         <is>
-          <t>872-594-168</t>
+          <t>871-889-118</t>
         </is>
       </c>
       <c r="BH413" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BI413" t="inlineStr">
-        <is>
-          <t>Mãe/pai</t>
-        </is>
-      </c>
-      <c r="BJ413" t="inlineStr">
-        <is>
-          <t>869-514-711</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BK413" t="inlineStr">
@@ -79501,17 +79515,22 @@
       </c>
       <c r="BL413" t="inlineStr">
         <is>
-          <t>Deslocado</t>
+          <t>VBG Interno</t>
         </is>
       </c>
       <c r="BM413" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>VBG Interno</t>
+        </is>
+      </c>
+      <c r="BN413" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="BO413" t="inlineStr">
         <is>
-          <t>PRJ_0425</t>
+          <t>PRJ_0579</t>
         </is>
       </c>
     </row>
@@ -79523,7 +79542,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>RAUDATE ALIASSE RAULO</t>
+          <t>RAFAEL SALIMO REBOTE</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -79558,7 +79577,7 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>021508876223I</t>
+          <t>030908884084A</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
@@ -79568,14 +79587,14 @@
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="L414">
         <v>2005</v>
       </c>
       <c r="M414">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N414" t="inlineStr">
         <is>
@@ -79584,7 +79603,7 @@
       </c>
       <c r="O414" t="inlineStr">
         <is>
-          <t>12a classe</t>
+          <t>10a classe</t>
         </is>
       </c>
       <c r="P414" t="inlineStr">
@@ -79594,12 +79613,12 @@
       </c>
       <c r="T414" t="inlineStr">
         <is>
-          <t>03/2020</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="U414" t="inlineStr">
         <is>
-          <t>PALMA</t>
+          <t>MEMBA</t>
         </is>
       </c>
       <c r="V414" t="inlineStr">
@@ -79614,12 +79633,7 @@
       </c>
       <c r="X414" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Y414" t="inlineStr">
-        <is>
-          <t>VENDAS DE REFEICOES</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="Z414" t="inlineStr">
@@ -79639,68 +79653,12 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AF414" t="inlineStr">
-        <is>
-          <t>RECEBI PRODUTOS ALIMENTARES.</t>
-        </is>
-      </c>
-      <c r="AG414">
-        <v>1</v>
-      </c>
-      <c r="AH414" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AJ414" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AL414" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AN414" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AP414" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AQ414" t="inlineStr">
-        <is>
-          <t>RECEBI MATERIAIS PARA MACHAMBAS (ENCHADA E SEMENTES).</t>
-        </is>
-      </c>
-      <c r="AR414">
-        <v>1</v>
-      </c>
-      <c r="AS414" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AU414" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AW414" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AY414" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BA414" t="inlineStr">
@@ -79710,17 +79668,12 @@
       </c>
       <c r="BB414" t="inlineStr">
         <is>
-          <t>868-944-882</t>
+          <t>877-297-168</t>
         </is>
       </c>
       <c r="BC414" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BD414" t="inlineStr">
-        <is>
-          <t>848-032-003</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BE414" t="inlineStr">
@@ -79735,12 +79688,22 @@
       </c>
       <c r="BG414" t="inlineStr">
         <is>
-          <t>866-594-972</t>
+          <t>872-594-168</t>
         </is>
       </c>
       <c r="BH414" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BI414" t="inlineStr">
+        <is>
+          <t>Mãe/pai</t>
+        </is>
+      </c>
+      <c r="BJ414" t="inlineStr">
+        <is>
+          <t>869-514-711</t>
         </is>
       </c>
       <c r="BK414" t="inlineStr">
@@ -79760,7 +79723,7 @@
       </c>
       <c r="BO414" t="inlineStr">
         <is>
-          <t>PRJ_0430</t>
+          <t>PRJ_0425</t>
         </is>
       </c>
     </row>
@@ -79772,7 +79735,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>ROSALINA JOHN MANUEL</t>
+          <t>RAUDATE ALIASSE RAULO</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -79807,7 +79770,7 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>021208875830A</t>
+          <t>021508876223I</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
@@ -79821,10 +79784,10 @@
         </is>
       </c>
       <c r="L415">
-        <v>1994</v>
+        <v>2005</v>
       </c>
       <c r="M415">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="N415" t="inlineStr">
         <is>
@@ -79833,40 +79796,32 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>9a classe</t>
+          <t>12a classe</t>
         </is>
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q415">
-        <v>3</v>
-      </c>
-      <c r="R415" t="inlineStr">
-        <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T415" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>03/2020</t>
         </is>
       </c>
       <c r="U415" t="inlineStr">
         <is>
-          <t>MUIDUMBI</t>
+          <t>PALMA</t>
         </is>
       </c>
       <c r="V415" t="inlineStr">
         <is>
-          <t>Sozinha/o com seu AF da sua origem</t>
+          <t>Familia acolhedora</t>
         </is>
       </c>
       <c r="W415" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="X415" t="inlineStr">
@@ -79876,7 +79831,7 @@
       </c>
       <c r="Y415" t="inlineStr">
         <is>
-          <t>VENDO BOLINHOS E CHINELOS</t>
+          <t>VENDAS DE REFEICOES</t>
         </is>
       </c>
       <c r="Z415" t="inlineStr">
@@ -79901,7 +79856,7 @@
       </c>
       <c r="AF415" t="inlineStr">
         <is>
-          <t>RECEBI TRIGO, BALDE, CAPULANA E PANELAS.</t>
+          <t>RECEBI PRODUTOS ALIMENTARES.</t>
         </is>
       </c>
       <c r="AG415">
@@ -79929,7 +79884,35 @@
       </c>
       <c r="AP415" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AQ415" t="inlineStr">
+        <is>
+          <t>RECEBI MATERIAIS PARA MACHAMBAS (ENCHADA E SEMENTES).</t>
+        </is>
+      </c>
+      <c r="AR415">
+        <v>1</v>
+      </c>
+      <c r="AS415" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AU415" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AW415" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AY415" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="BA415" t="inlineStr">
@@ -79939,7 +79922,7 @@
       </c>
       <c r="BB415" t="inlineStr">
         <is>
-          <t>868-406-085</t>
+          <t>868-944-882</t>
         </is>
       </c>
       <c r="BC415" t="inlineStr">
@@ -79949,7 +79932,7 @@
       </c>
       <c r="BD415" t="inlineStr">
         <is>
-          <t>840-658-281</t>
+          <t>848-032-003</t>
         </is>
       </c>
       <c r="BE415" t="inlineStr">
@@ -79959,12 +79942,12 @@
       </c>
       <c r="BF415" t="inlineStr">
         <is>
-          <t>Mãe/pai</t>
+          <t>Tio/a</t>
         </is>
       </c>
       <c r="BG415" t="inlineStr">
         <is>
-          <t>872-200-376</t>
+          <t>866-594-972</t>
         </is>
       </c>
       <c r="BH415" t="inlineStr">
@@ -79989,7 +79972,7 @@
       </c>
       <c r="BO415" t="inlineStr">
         <is>
-          <t>PRJ_0427</t>
+          <t>PRJ_0430</t>
         </is>
       </c>
     </row>
@@ -80001,7 +79984,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>SAMUEL ANSELMO MURURI</t>
+          <t>ROSALINA JOHN MANUEL</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -80036,7 +80019,7 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>031308878889B</t>
+          <t>021208875830A</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
@@ -80046,23 +80029,23 @@
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="L416">
-        <v>2003</v>
+        <v>1994</v>
       </c>
       <c r="M416">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="N416" t="inlineStr">
         <is>
-          <t>União marital</t>
+          <t>Solteria/o</t>
         </is>
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t>12a classe</t>
+          <t>9a classe</t>
         </is>
       </c>
       <c r="P416" t="inlineStr">
@@ -80071,36 +80054,89 @@
         </is>
       </c>
       <c r="Q416">
+        <v>3</v>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>11/2020</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>MUIDUMBI</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>Sozinha/o com seu AF da sua origem</t>
+        </is>
+      </c>
+      <c r="W416" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="X416" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Y416" t="inlineStr">
+        <is>
+          <t>VENDO BOLINHOS E CHINELOS</t>
+        </is>
+      </c>
+      <c r="Z416" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AA416" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AC416" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AE416" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AF416" t="inlineStr">
+        <is>
+          <t>RECEBI TRIGO, BALDE, CAPULANA E PANELAS.</t>
+        </is>
+      </c>
+      <c r="AG416">
         <v>1</v>
       </c>
-      <c r="R416" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="X416" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="Z416" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AA416" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AC416" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AE416" t="inlineStr">
-        <is>
-          <t>Não</t>
+      <c r="AH416" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AJ416" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AL416" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AN416" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="AP416" t="inlineStr">
@@ -80115,7 +80151,7 @@
       </c>
       <c r="BB416" t="inlineStr">
         <is>
-          <t>865-084-139</t>
+          <t>868-406-085</t>
         </is>
       </c>
       <c r="BC416" t="inlineStr">
@@ -80125,7 +80161,7 @@
       </c>
       <c r="BD416" t="inlineStr">
         <is>
-          <t>862-358-096</t>
+          <t>840-658-281</t>
         </is>
       </c>
       <c r="BE416" t="inlineStr">
@@ -80135,12 +80171,12 @@
       </c>
       <c r="BF416" t="inlineStr">
         <is>
-          <t>Irmã/o</t>
+          <t>Mãe/pai</t>
         </is>
       </c>
       <c r="BG416" t="inlineStr">
         <is>
-          <t>874-443-516</t>
+          <t>872-200-376</t>
         </is>
       </c>
       <c r="BH416" t="inlineStr">
@@ -80155,17 +80191,17 @@
       </c>
       <c r="BL416" t="inlineStr">
         <is>
-          <t>Familia acolhedora</t>
+          <t>Deslocado</t>
         </is>
       </c>
       <c r="BM416" t="inlineStr">
         <is>
-          <t>Acolhedora</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="BO416" t="inlineStr">
         <is>
-          <t>PRJ_0364</t>
+          <t>PRJ_0427</t>
         </is>
       </c>
     </row>
@@ -80177,7 +80213,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>SEVERINO LOURENCO HILARIO</t>
+          <t>SAMUEL ANSELMO MURURI</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -80212,7 +80248,7 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>021108885815S</t>
+          <t>031308878889B</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
@@ -80226,188 +80262,122 @@
         </is>
       </c>
       <c r="L417">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="M417">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N417" t="inlineStr">
         <is>
-          <t>Solteria/o</t>
+          <t>União marital</t>
         </is>
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t>9a classe</t>
+          <t>12a classe</t>
         </is>
       </c>
       <c r="P417" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="T417" t="inlineStr">
-        <is>
-          <t>07/2020</t>
-        </is>
-      </c>
-      <c r="U417" t="inlineStr">
-        <is>
-          <t>MUEDA</t>
-        </is>
-      </c>
-      <c r="V417" t="inlineStr">
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q417">
+        <v>1</v>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="X417" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="Z417" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AA417" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AC417" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AE417" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AP417" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="BA417" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BB417" t="inlineStr">
+        <is>
+          <t>865-084-139</t>
+        </is>
+      </c>
+      <c r="BC417" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BD417" t="inlineStr">
+        <is>
+          <t>862-358-096</t>
+        </is>
+      </c>
+      <c r="BE417" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BF417" t="inlineStr">
+        <is>
+          <t>Irmã/o</t>
+        </is>
+      </c>
+      <c r="BG417" t="inlineStr">
+        <is>
+          <t>874-443-516</t>
+        </is>
+      </c>
+      <c r="BH417" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="BK417" t="inlineStr">
+        <is>
+          <t>Número proprio</t>
+        </is>
+      </c>
+      <c r="BL417" t="inlineStr">
         <is>
           <t>Familia acolhedora</t>
         </is>
       </c>
-      <c r="W417" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="X417" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="Z417" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AA417" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AC417" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AE417" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AF417" t="inlineStr">
-        <is>
-          <t>PRODUTOS ALIMENTARES</t>
-        </is>
-      </c>
-      <c r="AG417">
-        <v>1</v>
-      </c>
-      <c r="AH417" t="inlineStr">
-        <is>
-          <t>MATERIAL PARA USO DOMÉSTICO</t>
-        </is>
-      </c>
-      <c r="AI417">
-        <v>2</v>
-      </c>
-      <c r="AJ417" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AL417" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AN417" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AP417" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AQ417" t="inlineStr">
-        <is>
-          <t>INSUMOS AGRICOLA</t>
-        </is>
-      </c>
-      <c r="AR417">
-        <v>1</v>
-      </c>
-      <c r="AS417" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AU417" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AW417" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AY417" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="BA417" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BB417" t="inlineStr">
-        <is>
-          <t>862-024-727</t>
-        </is>
-      </c>
-      <c r="BC417" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="BE417" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BF417" t="inlineStr">
-        <is>
-          <t>Mãe/pai</t>
-        </is>
-      </c>
-      <c r="BG417" t="inlineStr">
-        <is>
-          <t>866-616-371</t>
-        </is>
-      </c>
-      <c r="BH417" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="BK417" t="inlineStr">
-        <is>
-          <t>Número proprio</t>
-        </is>
-      </c>
-      <c r="BL417" t="inlineStr">
-        <is>
-          <t>Deslocado</t>
-        </is>
-      </c>
       <c r="BM417" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Acolhedora</t>
         </is>
       </c>
       <c r="BO417" t="inlineStr">
         <is>
-          <t>PRJ_0475</t>
+          <t>PRJ_0364</t>
         </is>
       </c>
     </row>
@@ -80419,7 +80389,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>TANIA JORGE ABACAR</t>
+          <t>SEVERINO LOURENCO HILARIO</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -80454,7 +80424,7 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>031307234140A</t>
+          <t>021108885815S</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
@@ -80464,14 +80434,14 @@
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="L418">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="M418">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N418" t="inlineStr">
         <is>
@@ -80480,7 +80450,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>12a classe</t>
+          <t>9a classe</t>
         </is>
       </c>
       <c r="P418" t="inlineStr">
@@ -80488,6 +80458,26 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>07/2020</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>MUEDA</t>
+        </is>
+      </c>
+      <c r="V418" t="inlineStr">
+        <is>
+          <t>Familia acolhedora</t>
+        </is>
+      </c>
+      <c r="W418" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="X418" t="inlineStr">
         <is>
           <t>Não</t>
@@ -80510,12 +80500,71 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AF418" t="inlineStr">
+        <is>
+          <t>PRODUTOS ALIMENTARES</t>
+        </is>
+      </c>
+      <c r="AG418">
+        <v>1</v>
+      </c>
+      <c r="AH418" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA USO DOMÉSTICO</t>
+        </is>
+      </c>
+      <c r="AI418">
+        <v>2</v>
+      </c>
+      <c r="AJ418" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AL418" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AN418" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="AP418" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AQ418" t="inlineStr">
+        <is>
+          <t>INSUMOS AGRICOLA</t>
+        </is>
+      </c>
+      <c r="AR418">
+        <v>1</v>
+      </c>
+      <c r="AS418" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AU418" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AW418" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AY418" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="BA418" t="inlineStr">
@@ -80525,17 +80574,12 @@
       </c>
       <c r="BB418" t="inlineStr">
         <is>
-          <t>870-008-872</t>
+          <t>862-024-727</t>
         </is>
       </c>
       <c r="BC418" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BD418" t="inlineStr">
-        <is>
-          <t>852-990-247</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BE418" t="inlineStr">
@@ -80550,22 +80594,12 @@
       </c>
       <c r="BG418" t="inlineStr">
         <is>
-          <t>868-664-893</t>
+          <t>866-616-371</t>
         </is>
       </c>
       <c r="BH418" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BI418" t="inlineStr">
-        <is>
-          <t>Mãe/pai</t>
-        </is>
-      </c>
-      <c r="BJ418" t="inlineStr">
-        <is>
-          <t>846-860-706</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BK418" t="inlineStr">
@@ -80575,22 +80609,17 @@
       </c>
       <c r="BL418" t="inlineStr">
         <is>
-          <t>VBG Interno</t>
+          <t>Deslocado</t>
         </is>
       </c>
       <c r="BM418" t="inlineStr">
         <is>
-          <t>VBG Interno</t>
-        </is>
-      </c>
-      <c r="BN418" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="BO418" t="inlineStr">
         <is>
-          <t>PRJ_0562</t>
+          <t>PRJ_0475</t>
         </is>
       </c>
     </row>
@@ -80602,7 +80631,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>TERESA MUSSA CHABANE</t>
+          <t>TANIA JORGE ABACAR</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -80637,7 +80666,7 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>021208883994P</t>
+          <t>031307234140A</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
@@ -80654,7 +80683,7 @@
         <v>2005</v>
       </c>
       <c r="M419">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N419" t="inlineStr">
         <is>
@@ -80663,50 +80692,17 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>8a classe</t>
+          <t>12a classe</t>
         </is>
       </c>
       <c r="P419" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q419">
-        <v>1</v>
-      </c>
-      <c r="R419" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="T419" t="inlineStr">
-        <is>
-          <t>11/2020</t>
-        </is>
-      </c>
-      <c r="U419" t="inlineStr">
-        <is>
-          <t>MUIDUMBE</t>
-        </is>
-      </c>
-      <c r="V419" t="inlineStr">
-        <is>
-          <t>Sozinha/o com seu AF da sua origem</t>
-        </is>
-      </c>
-      <c r="W419" t="inlineStr">
-        <is>
           <t>Não</t>
         </is>
       </c>
       <c r="X419" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Y419" t="inlineStr">
-        <is>
-          <t>VENDA DE BADJIAS</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="Z419" t="inlineStr">
@@ -80716,12 +80712,7 @@
       </c>
       <c r="AA419" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AB419" t="inlineStr">
-        <is>
-          <t>POLIO( VACINACAO DE CRIANCAS)</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AC419" t="inlineStr">
@@ -80731,35 +80722,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AF419" t="inlineStr">
-        <is>
-          <t>EQUIPAMENTOS DA COZINHA E VESTUARIO</t>
-        </is>
-      </c>
-      <c r="AG419">
-        <v>1</v>
-      </c>
-      <c r="AH419" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AJ419" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AL419" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AN419" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AP419" t="inlineStr">
@@ -80774,12 +80737,17 @@
       </c>
       <c r="BB419" t="inlineStr">
         <is>
-          <t>876-368-239</t>
+          <t>870-008-872</t>
         </is>
       </c>
       <c r="BC419" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BD419" t="inlineStr">
+        <is>
+          <t>852-990-247</t>
         </is>
       </c>
       <c r="BE419" t="inlineStr">
@@ -80794,12 +80762,22 @@
       </c>
       <c r="BG419" t="inlineStr">
         <is>
-          <t>860-426-063</t>
+          <t>868-664-893</t>
         </is>
       </c>
       <c r="BH419" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BI419" t="inlineStr">
+        <is>
+          <t>Mãe/pai</t>
+        </is>
+      </c>
+      <c r="BJ419" t="inlineStr">
+        <is>
+          <t>846-860-706</t>
         </is>
       </c>
       <c r="BK419" t="inlineStr">
@@ -80809,12 +80787,12 @@
       </c>
       <c r="BL419" t="inlineStr">
         <is>
-          <t>Deslocado</t>
+          <t>VBG Interno</t>
         </is>
       </c>
       <c r="BM419" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>VBG Interno</t>
         </is>
       </c>
       <c r="BN419" t="inlineStr">
@@ -80824,7 +80802,7 @@
       </c>
       <c r="BO419" t="inlineStr">
         <is>
-          <t>PRJ_0479</t>
+          <t>PRJ_0562</t>
         </is>
       </c>
     </row>
@@ -80836,7 +80814,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>VERONICA SIMAO FABIAO</t>
+          <t>TERESA MUSSA CHABANE</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -80871,7 +80849,7 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>030708877721C</t>
+          <t>021208883994P</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
@@ -80885,10 +80863,10 @@
         </is>
       </c>
       <c r="L420">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="M420">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N420" t="inlineStr">
         <is>
@@ -80897,7 +80875,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>9a classe</t>
+          <t>8a classe</t>
         </is>
       </c>
       <c r="P420" t="inlineStr">
@@ -80906,7 +80884,7 @@
         </is>
       </c>
       <c r="Q420">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R420" t="inlineStr">
         <is>
@@ -80915,12 +80893,12 @@
       </c>
       <c r="T420" t="inlineStr">
         <is>
-          <t>04/2020</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="U420" t="inlineStr">
         <is>
-          <t>MUATITI</t>
+          <t>MUIDUMBE</t>
         </is>
       </c>
       <c r="V420" t="inlineStr">
@@ -80930,22 +80908,32 @@
       </c>
       <c r="W420" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="X420" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Y420" t="inlineStr">
+        <is>
+          <t>VENDA DE BADJIAS</t>
         </is>
       </c>
       <c r="Z420" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AA420" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AB420" t="inlineStr">
+        <is>
+          <t>POLIO( VACINACAO DE CRIANCAS)</t>
         </is>
       </c>
       <c r="AC420" t="inlineStr">
@@ -80960,7 +80948,7 @@
       </c>
       <c r="AF420" t="inlineStr">
         <is>
-          <t>RECEBI PRODUTOS ALIMENTARES</t>
+          <t>EQUIPAMENTOS DA COZINHA E VESTUARIO</t>
         </is>
       </c>
       <c r="AG420">
@@ -80968,11 +80956,8 @@
       </c>
       <c r="AH420" t="inlineStr">
         <is>
-          <t>RECEBI PANELAS DA VISAO MUNDIAL</t>
-        </is>
-      </c>
-      <c r="AI420">
-        <v>2</v>
+          <t>##N/A##</t>
+        </is>
       </c>
       <c r="AJ420" t="inlineStr">
         <is>
@@ -81001,7 +80986,7 @@
       </c>
       <c r="BB420" t="inlineStr">
         <is>
-          <t>869-296-409</t>
+          <t>876-368-239</t>
         </is>
       </c>
       <c r="BC420" t="inlineStr">
@@ -81021,7 +81006,7 @@
       </c>
       <c r="BG420" t="inlineStr">
         <is>
-          <t>875-865-492</t>
+          <t>860-426-063</t>
         </is>
       </c>
       <c r="BH420" t="inlineStr">
@@ -81044,9 +81029,14 @@
           <t>IDP</t>
         </is>
       </c>
+      <c r="BN420" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
       <c r="BO420" t="inlineStr">
         <is>
-          <t>PRJ_0436</t>
+          <t>PRJ_0479</t>
         </is>
       </c>
     </row>
@@ -81058,7 +81048,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>ALBERTO ANTONIO TRINTA MUJUA</t>
+          <t>VERONICA SIMAO FABIAO</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -81093,7 +81083,7 @@
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>031308868715F</t>
+          <t>030708877721C</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
@@ -81103,14 +81093,14 @@
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="L421">
-        <v>1999</v>
+        <v>2004</v>
       </c>
       <c r="M421">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="N421" t="inlineStr">
         <is>
@@ -81119,7 +81109,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>11a classe</t>
+          <t>9a classe</t>
         </is>
       </c>
       <c r="P421" t="inlineStr">
@@ -81128,21 +81118,36 @@
         </is>
       </c>
       <c r="Q421">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R421" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>04/2020</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>MUATITI</t>
+        </is>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>Sozinha/o com seu AF da sua origem</t>
+        </is>
+      </c>
+      <c r="W421" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="X421" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Y421" t="inlineStr">
-        <is>
-          <t>AGENTE E-MOLA</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="Z421" t="inlineStr">
@@ -81167,7 +81172,7 @@
       </c>
       <c r="AF421" t="inlineStr">
         <is>
-          <t>PRODUTOS PARA USO DOMÉSTICO</t>
+          <t>RECEBI PRODUTOS ALIMENTARES</t>
         </is>
       </c>
       <c r="AG421">
@@ -81175,7 +81180,7 @@
       </c>
       <c r="AH421" t="inlineStr">
         <is>
-          <t>PRODUTOS ALIMENTARES</t>
+          <t>RECEBI PANELAS DA VISAO MUNDIAL</t>
         </is>
       </c>
       <c r="AI421">
@@ -81198,35 +81203,7 @@
       </c>
       <c r="AP421" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AQ421" t="inlineStr">
-        <is>
-          <t>INSUMOS AGRICOLA</t>
-        </is>
-      </c>
-      <c r="AR421">
-        <v>1</v>
-      </c>
-      <c r="AS421" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AU421" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AW421" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AY421" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BA421" t="inlineStr">
@@ -81236,7 +81213,7 @@
       </c>
       <c r="BB421" t="inlineStr">
         <is>
-          <t>876-964-537</t>
+          <t>869-296-409</t>
         </is>
       </c>
       <c r="BC421" t="inlineStr">
@@ -81251,12 +81228,12 @@
       </c>
       <c r="BF421" t="inlineStr">
         <is>
-          <t>Irmã/o</t>
+          <t>Mãe/pai</t>
         </is>
       </c>
       <c r="BG421" t="inlineStr">
         <is>
-          <t>879-856-493</t>
+          <t>875-865-492</t>
         </is>
       </c>
       <c r="BH421" t="inlineStr">
@@ -81271,22 +81248,17 @@
       </c>
       <c r="BL421" t="inlineStr">
         <is>
-          <t>Familia acolhedora</t>
+          <t>Deslocado</t>
         </is>
       </c>
       <c r="BM421" t="inlineStr">
         <is>
-          <t>Acolhedora</t>
-        </is>
-      </c>
-      <c r="BN421" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="BO421" t="inlineStr">
         <is>
-          <t>PRJ_0368</t>
+          <t>PRJ_0436</t>
         </is>
       </c>
     </row>
@@ -81298,7 +81270,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>ALBINO CRISANTO AREDO</t>
+          <t>ALBERTO ANTONIO TRINTA MUJUA</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -81333,7 +81305,7 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>02140886881D</t>
+          <t>031308868715F</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
@@ -81347,19 +81319,19 @@
         </is>
       </c>
       <c r="L422">
-        <v>1994</v>
+        <v>1999</v>
       </c>
       <c r="M422">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="N422" t="inlineStr">
         <is>
-          <t>Casada/o</t>
+          <t>Solteria/o</t>
         </is>
       </c>
       <c r="O422" t="inlineStr">
         <is>
-          <t>7a classe</t>
+          <t>11a classe</t>
         </is>
       </c>
       <c r="P422" t="inlineStr">
@@ -81368,41 +81340,26 @@
         </is>
       </c>
       <c r="Q422">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R422" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="T422" t="inlineStr">
-        <is>
-          <t>09/2022</t>
-        </is>
-      </c>
-      <c r="U422" t="inlineStr">
-        <is>
-          <t>MUIDUMBE</t>
-        </is>
-      </c>
-      <c r="V422" t="inlineStr">
-        <is>
-          <t>Familia acolhedora</t>
-        </is>
-      </c>
-      <c r="W422" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="X422" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Y422" t="inlineStr">
+        <is>
+          <t>AGENTE E-MOLA</t>
         </is>
       </c>
       <c r="Z422" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="AA422" t="inlineStr">
@@ -81422,7 +81379,7 @@
       </c>
       <c r="AF422" t="inlineStr">
         <is>
-          <t>COBERTORES</t>
+          <t>PRODUTOS PARA USO DOMÉSTICO</t>
         </is>
       </c>
       <c r="AG422">
@@ -81430,7 +81387,7 @@
       </c>
       <c r="AH422" t="inlineStr">
         <is>
-          <t>MATERIAL PARA USO DOMÉSTICO</t>
+          <t>PRODUTOS ALIMENTARES</t>
         </is>
       </c>
       <c r="AI422">
@@ -81453,7 +81410,35 @@
       </c>
       <c r="AP422" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AQ422" t="inlineStr">
+        <is>
+          <t>INSUMOS AGRICOLA</t>
+        </is>
+      </c>
+      <c r="AR422">
+        <v>1</v>
+      </c>
+      <c r="AS422" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AU422" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AW422" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AY422" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="BA422" t="inlineStr">
@@ -81463,7 +81448,7 @@
       </c>
       <c r="BB422" t="inlineStr">
         <is>
-          <t>867-525-866</t>
+          <t>876-964-537</t>
         </is>
       </c>
       <c r="BC422" t="inlineStr">
@@ -81478,27 +81463,17 @@
       </c>
       <c r="BF422" t="inlineStr">
         <is>
-          <t>Mãe/pai</t>
+          <t>Irmã/o</t>
         </is>
       </c>
       <c r="BG422" t="inlineStr">
         <is>
-          <t>876-357-044</t>
+          <t>879-856-493</t>
         </is>
       </c>
       <c r="BH422" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BI422" t="inlineStr">
-        <is>
-          <t>Esposo/a</t>
-        </is>
-      </c>
-      <c r="BJ422" t="inlineStr">
-        <is>
-          <t>861-669-275</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BK422" t="inlineStr">
@@ -81508,17 +81483,22 @@
       </c>
       <c r="BL422" t="inlineStr">
         <is>
-          <t>Deslocado</t>
+          <t>Familia acolhedora</t>
         </is>
       </c>
       <c r="BM422" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Acolhedora</t>
+        </is>
+      </c>
+      <c r="BN422" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="BO422" t="inlineStr">
         <is>
-          <t>PRJ_0511</t>
+          <t>PRJ_0368</t>
         </is>
       </c>
     </row>
@@ -81530,7 +81510,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>ANGELINO JOAO</t>
+          <t>ALBINO CRISANTO AREDO</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -81545,12 +81525,12 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Costa Marques &amp; Otilia Passiel</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Turma 7</t>
+          <t>Turma 6</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
@@ -81565,7 +81545,7 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>020908900187C</t>
+          <t>02140886881D</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
@@ -81579,39 +81559,47 @@
         </is>
       </c>
       <c r="L423">
-        <v>2000</v>
+        <v>1994</v>
       </c>
       <c r="M423">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N423" t="inlineStr">
         <is>
-          <t>Solteria/o</t>
+          <t>Casada/o</t>
         </is>
       </c>
       <c r="O423" t="inlineStr">
         <is>
-          <t>10a classe</t>
+          <t>7a classe</t>
         </is>
       </c>
       <c r="P423" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q423">
+        <v>2</v>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T423" t="inlineStr">
         <is>
-          <t>8/2019</t>
+          <t>09/2022</t>
         </is>
       </c>
       <c r="U423" t="inlineStr">
         <is>
-          <t>MOCIMBOA DA PRAIA</t>
+          <t>MUIDUMBE</t>
         </is>
       </c>
       <c r="V423" t="inlineStr">
         <is>
-          <t>Sozinha/o com seu AF da sua origem</t>
+          <t>Familia acolhedora</t>
         </is>
       </c>
       <c r="W423" t="inlineStr">
@@ -81646,7 +81634,7 @@
       </c>
       <c r="AF423" t="inlineStr">
         <is>
-          <t>PRODUTOS ALIMENTARES</t>
+          <t>COBERTORES</t>
         </is>
       </c>
       <c r="AG423">
@@ -81654,55 +81642,30 @@
       </c>
       <c r="AH423" t="inlineStr">
         <is>
+          <t>MATERIAL PARA USO DOMÉSTICO</t>
+        </is>
+      </c>
+      <c r="AI423">
+        <v>2</v>
+      </c>
+      <c r="AJ423" t="inlineStr">
+        <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AJ423" t="inlineStr">
+      <c r="AL423" t="inlineStr">
         <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AL423" t="inlineStr">
+      <c r="AN423" t="inlineStr">
         <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AN423" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
       <c r="AP423" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AQ423" t="inlineStr">
-        <is>
-          <t>INSUMOS AGRICOLAS (SEMENTES), MATERIAL DA MACHAMBA (ENCHADA, CATANA</t>
-        </is>
-      </c>
-      <c r="AR423">
-        <v>1</v>
-      </c>
-      <c r="AS423" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AU423" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AW423" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AY423" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BA423" t="inlineStr">
@@ -81712,17 +81675,12 @@
       </c>
       <c r="BB423" t="inlineStr">
         <is>
-          <t>861-852-647</t>
+          <t>867-525-866</t>
         </is>
       </c>
       <c r="BC423" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BD423" t="inlineStr">
-        <is>
-          <t>862-517-361</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BE423" t="inlineStr">
@@ -81732,17 +81690,27 @@
       </c>
       <c r="BF423" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Mãe/pai</t>
         </is>
       </c>
       <c r="BG423" t="inlineStr">
         <is>
-          <t>871-883-880</t>
+          <t>876-357-044</t>
         </is>
       </c>
       <c r="BH423" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BI423" t="inlineStr">
+        <is>
+          <t>Esposo/a</t>
+        </is>
+      </c>
+      <c r="BJ423" t="inlineStr">
+        <is>
+          <t>861-669-275</t>
         </is>
       </c>
       <c r="BK423" t="inlineStr">
@@ -81762,7 +81730,7 @@
       </c>
       <c r="BO423" t="inlineStr">
         <is>
-          <t>PRJ_0495</t>
+          <t>PRJ_0511</t>
         </is>
       </c>
     </row>
@@ -81774,7 +81742,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>ATIA JAMAL EUSEBIO SILVA</t>
+          <t>ANGELINO JOAO</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -81789,7 +81757,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -81809,7 +81777,7 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>031308875634J</t>
+          <t>020908900187C</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
@@ -81819,14 +81787,14 @@
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="L424">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="M424">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N424" t="inlineStr">
         <is>
@@ -81835,7 +81803,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t>12a classe</t>
+          <t>10a classe</t>
         </is>
       </c>
       <c r="P424" t="inlineStr">
@@ -81845,12 +81813,12 @@
       </c>
       <c r="T424" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>8/2019</t>
         </is>
       </c>
       <c r="U424" t="inlineStr">
         <is>
-          <t>ANCUABE</t>
+          <t>MOCIMBOA DA PRAIA</t>
         </is>
       </c>
       <c r="V424" t="inlineStr">
@@ -81865,12 +81833,7 @@
       </c>
       <c r="X424" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Y424" t="inlineStr">
-        <is>
-          <t>VENDO BOLINHOS</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="Z424" t="inlineStr">
@@ -81928,7 +81891,7 @@
       </c>
       <c r="AQ424" t="inlineStr">
         <is>
-          <t>INSUMOS AGRICOLAS (SEMENTES) E MATERIAL DA MACHAMBA (ENCHADA)</t>
+          <t>INSUMOS AGRICOLAS (SEMENTES), MATERIAL DA MACHAMBA (ENCHADA, CATANA</t>
         </is>
       </c>
       <c r="AR424">
@@ -81961,12 +81924,17 @@
       </c>
       <c r="BB424" t="inlineStr">
         <is>
-          <t>870-529-272</t>
+          <t>861-852-647</t>
         </is>
       </c>
       <c r="BC424" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BD424" t="inlineStr">
+        <is>
+          <t>862-517-361</t>
         </is>
       </c>
       <c r="BE424" t="inlineStr">
@@ -81976,12 +81944,12 @@
       </c>
       <c r="BF424" t="inlineStr">
         <is>
-          <t>Mãe/pai</t>
+          <t>Outro</t>
         </is>
       </c>
       <c r="BG424" t="inlineStr">
         <is>
-          <t>876-892-400</t>
+          <t>871-883-880</t>
         </is>
       </c>
       <c r="BH424" t="inlineStr">
@@ -82006,7 +81974,7 @@
       </c>
       <c r="BO424" t="inlineStr">
         <is>
-          <t>PRJ_0494</t>
+          <t>PRJ_0495</t>
         </is>
       </c>
     </row>
@@ -82018,7 +81986,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>CARLITOS CHARAMA JOAQUIM ALFANO</t>
+          <t>ATIA JAMAL EUSEBIO SILVA</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -82033,7 +82001,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -82053,7 +82021,7 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>031308870601F</t>
+          <t>031308875634J</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
@@ -82063,41 +82031,58 @@
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="L425">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="M425">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N425" t="inlineStr">
         <is>
-          <t>Casada/o</t>
+          <t>Solteria/o</t>
         </is>
       </c>
       <c r="O425" t="inlineStr">
         <is>
-          <t>9a classe</t>
+          <t>12a classe</t>
         </is>
       </c>
       <c r="P425" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q425">
-        <v>2</v>
-      </c>
-      <c r="R425" t="inlineStr">
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>11/2025</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>ANCUABE</t>
+        </is>
+      </c>
+      <c r="V425" t="inlineStr">
+        <is>
+          <t>Sozinha/o com seu AF da sua origem</t>
+        </is>
+      </c>
+      <c r="W425" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="X425" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Y425" t="inlineStr">
+        <is>
+          <t>VENDO BOLINHOS</t>
         </is>
       </c>
       <c r="Z425" t="inlineStr">
@@ -82117,16 +82102,82 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AF425" t="inlineStr">
+        <is>
+          <t>PRODUTOS ALIMENTARES</t>
+        </is>
+      </c>
+      <c r="AG425">
+        <v>1</v>
+      </c>
+      <c r="AH425" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AJ425" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AL425" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AN425" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="AP425" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AQ425" t="inlineStr">
+        <is>
+          <t>INSUMOS AGRICOLAS (SEMENTES) E MATERIAL DA MACHAMBA (ENCHADA)</t>
+        </is>
+      </c>
+      <c r="AR425">
+        <v>1</v>
+      </c>
+      <c r="AS425" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AU425" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AW425" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AY425" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="BA425" t="inlineStr">
         <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BB425" t="inlineStr">
+        <is>
+          <t>870-529-272</t>
+        </is>
+      </c>
+      <c r="BC425" t="inlineStr">
+        <is>
           <t>Não</t>
         </is>
       </c>
@@ -82137,12 +82188,12 @@
       </c>
       <c r="BF425" t="inlineStr">
         <is>
-          <t>Tio/a</t>
+          <t>Mãe/pai</t>
         </is>
       </c>
       <c r="BG425" t="inlineStr">
         <is>
-          <t>870-844-441</t>
+          <t>876-892-400</t>
         </is>
       </c>
       <c r="BH425" t="inlineStr">
@@ -82152,27 +82203,22 @@
       </c>
       <c r="BK425" t="inlineStr">
         <is>
-          <t>Número alternativo</t>
+          <t>Número proprio</t>
         </is>
       </c>
       <c r="BL425" t="inlineStr">
         <is>
-          <t>Familia acolhedora</t>
+          <t>Deslocado</t>
         </is>
       </c>
       <c r="BM425" t="inlineStr">
         <is>
-          <t>Acolhedora</t>
-        </is>
-      </c>
-      <c r="BN425" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="BO425" t="inlineStr">
         <is>
-          <t>PRJ_0372</t>
+          <t>PRJ_0494</t>
         </is>
       </c>
     </row>
@@ -82184,7 +82230,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>DANIEL JOSE</t>
+          <t>CARLITOS CHARAMA JOAQUIM ALFANO</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -82199,7 +82245,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -82214,12 +82260,12 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Cartão de Eleitor</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>095477-19032468008(091662-01/305)</t>
+          <t>031308870601F</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
@@ -82233,10 +82279,10 @@
         </is>
       </c>
       <c r="L426">
-        <v>1992</v>
+        <v>2002</v>
       </c>
       <c r="M426">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N426" t="inlineStr">
         <is>
@@ -82245,7 +82291,7 @@
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t>8a classe</t>
+          <t>9a classe</t>
         </is>
       </c>
       <c r="P426" t="inlineStr">
@@ -82254,33 +82300,13 @@
         </is>
       </c>
       <c r="Q426">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R426" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="T426" t="inlineStr">
-        <is>
-          <t>11/2020</t>
-        </is>
-      </c>
-      <c r="U426" t="inlineStr">
-        <is>
-          <t>MUIDUMBE</t>
-        </is>
-      </c>
-      <c r="V426" t="inlineStr">
-        <is>
-          <t>Sozinha/o com seu AF da sua origem</t>
-        </is>
-      </c>
-      <c r="W426" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="X426" t="inlineStr">
         <is>
           <t>Não</t>
@@ -82288,7 +82314,7 @@
       </c>
       <c r="Z426" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AA426" t="inlineStr">
@@ -82313,22 +82339,7 @@
       </c>
       <c r="BA426" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BB426" t="inlineStr">
-        <is>
-          <t>868-789-962</t>
-        </is>
-      </c>
-      <c r="BC426" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BD426" t="inlineStr">
-        <is>
-          <t>846-007-279</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BE426" t="inlineStr">
@@ -82338,12 +82349,12 @@
       </c>
       <c r="BF426" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Tio/a</t>
         </is>
       </c>
       <c r="BG426" t="inlineStr">
         <is>
-          <t>840-215-625</t>
+          <t>870-844-441</t>
         </is>
       </c>
       <c r="BH426" t="inlineStr">
@@ -82353,22 +82364,27 @@
       </c>
       <c r="BK426" t="inlineStr">
         <is>
-          <t>Número proprio</t>
+          <t>Número alternativo</t>
         </is>
       </c>
       <c r="BL426" t="inlineStr">
         <is>
-          <t>Deslocado</t>
+          <t>Familia acolhedora</t>
         </is>
       </c>
       <c r="BM426" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Acolhedora</t>
+        </is>
+      </c>
+      <c r="BN426" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="BO426" t="inlineStr">
         <is>
-          <t>PRJ_0512</t>
+          <t>PRJ_0372</t>
         </is>
       </c>
     </row>
@@ -82380,7 +82396,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>EMONE VICTORINO LUIS VIDAL</t>
+          <t>DANIEL JOSE</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -82395,7 +82411,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -82410,12 +82426,12 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>Cartão de Eleitor</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>031305235719J</t>
+          <t>095477-19032468008(091662-01/305)</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
@@ -82429,19 +82445,19 @@
         </is>
       </c>
       <c r="L427">
-        <v>1996</v>
+        <v>1992</v>
       </c>
       <c r="M427">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t>Solteria/o</t>
+          <t>Casada/o</t>
         </is>
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>12a classe</t>
+          <t>8a classe</t>
         </is>
       </c>
       <c r="P427" t="inlineStr">
@@ -82450,13 +82466,33 @@
         </is>
       </c>
       <c r="Q427">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R427" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>11/2020</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>MUIDUMBE</t>
+        </is>
+      </c>
+      <c r="V427" t="inlineStr">
+        <is>
+          <t>Sozinha/o com seu AF da sua origem</t>
+        </is>
+      </c>
+      <c r="W427" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="X427" t="inlineStr">
         <is>
           <t>Não</t>
@@ -82479,35 +82515,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AF427" t="inlineStr">
-        <is>
-          <t>RECEBI MATERIAIS DOMESTICOS (BALDES, PANELAS )</t>
-        </is>
-      </c>
-      <c r="AG427">
-        <v>2</v>
-      </c>
-      <c r="AH427" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AJ427" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AL427" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AN427" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AP427" t="inlineStr">
@@ -82522,7 +82530,7 @@
       </c>
       <c r="BB427" t="inlineStr">
         <is>
-          <t>864-526-166</t>
+          <t>868-789-962</t>
         </is>
       </c>
       <c r="BC427" t="inlineStr">
@@ -82532,7 +82540,7 @@
       </c>
       <c r="BD427" t="inlineStr">
         <is>
-          <t>844-103-057</t>
+          <t>846-007-279</t>
         </is>
       </c>
       <c r="BE427" t="inlineStr">
@@ -82542,27 +82550,17 @@
       </c>
       <c r="BF427" t="inlineStr">
         <is>
-          <t>Mãe/pai</t>
+          <t>Outro</t>
         </is>
       </c>
       <c r="BG427" t="inlineStr">
         <is>
-          <t>869-341-649</t>
+          <t>840-215-625</t>
         </is>
       </c>
       <c r="BH427" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BI427" t="inlineStr">
-        <is>
-          <t>Mãe/pai</t>
-        </is>
-      </c>
-      <c r="BJ427" t="inlineStr">
-        <is>
-          <t>853-159-559</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BK427" t="inlineStr">
@@ -82572,17 +82570,17 @@
       </c>
       <c r="BL427" t="inlineStr">
         <is>
-          <t>Familia acolhedora</t>
+          <t>Deslocado</t>
         </is>
       </c>
       <c r="BM427" t="inlineStr">
         <is>
-          <t>Acolhedora</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="BO427" t="inlineStr">
         <is>
-          <t>PRJ_0379</t>
+          <t>PRJ_0512</t>
         </is>
       </c>
     </row>
@@ -82594,7 +82592,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>EUGENIA HIBRAHIN MAICO</t>
+          <t>EMONE VICTORINO LUIS VIDAL</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -82609,7 +82607,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -82629,7 +82627,7 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>020106295276Q</t>
+          <t>031305235719J</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
@@ -82639,18 +82637,18 @@
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="L428">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="M428">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t>Casada/o</t>
+          <t>Solteria/o</t>
         </is>
       </c>
       <c r="O428" t="inlineStr">
@@ -82664,33 +82662,13 @@
         </is>
       </c>
       <c r="Q428">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R428" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="T428" t="inlineStr">
-        <is>
-          <t>05/2020</t>
-        </is>
-      </c>
-      <c r="U428" t="inlineStr">
-        <is>
-          <t>MUIDUMBE</t>
-        </is>
-      </c>
-      <c r="V428" t="inlineStr">
-        <is>
-          <t>Sozinha/o com seu AF da sua origem</t>
-        </is>
-      </c>
-      <c r="W428" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="X428" t="inlineStr">
         <is>
           <t>Não</t>
@@ -82698,7 +82676,7 @@
       </c>
       <c r="Z428" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="AA428" t="inlineStr">
@@ -82718,11 +82696,11 @@
       </c>
       <c r="AF428" t="inlineStr">
         <is>
-          <t>PRODUTOS ALIMENTAR, VESTUARIO E EQUIPAMENTOS DA COZINHAR</t>
+          <t>RECEBI MATERIAIS DOMESTICOS (BALDES, PANELAS )</t>
         </is>
       </c>
       <c r="AG428">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH428" t="inlineStr">
         <is>
@@ -82756,12 +82734,17 @@
       </c>
       <c r="BB428" t="inlineStr">
         <is>
-          <t>864-811-102</t>
+          <t>864-526-166</t>
         </is>
       </c>
       <c r="BC428" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BD428" t="inlineStr">
+        <is>
+          <t>844-103-057</t>
         </is>
       </c>
       <c r="BE428" t="inlineStr">
@@ -82771,17 +82754,27 @@
       </c>
       <c r="BF428" t="inlineStr">
         <is>
-          <t>Irmã/o</t>
+          <t>Mãe/pai</t>
         </is>
       </c>
       <c r="BG428" t="inlineStr">
         <is>
-          <t>853-445-534</t>
+          <t>869-341-649</t>
         </is>
       </c>
       <c r="BH428" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BI428" t="inlineStr">
+        <is>
+          <t>Mãe/pai</t>
+        </is>
+      </c>
+      <c r="BJ428" t="inlineStr">
+        <is>
+          <t>853-159-559</t>
         </is>
       </c>
       <c r="BK428" t="inlineStr">
@@ -82791,17 +82784,17 @@
       </c>
       <c r="BL428" t="inlineStr">
         <is>
-          <t>Deslocado</t>
+          <t>Familia acolhedora</t>
         </is>
       </c>
       <c r="BM428" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Acolhedora</t>
         </is>
       </c>
       <c r="BO428" t="inlineStr">
         <is>
-          <t>PRJ_0520</t>
+          <t>PRJ_0379</t>
         </is>
       </c>
     </row>
@@ -82813,7 +82806,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>EUGENIO ANTONIO</t>
+          <t>EUGENIA HIBRAHIN MAICO</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -82828,7 +82821,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -82843,12 +82836,12 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Cartão de Eleitor</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>092216-14052341213(090775-03/135)</t>
+          <t>020106295276Q</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
@@ -82858,14 +82851,14 @@
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="L429">
-        <v>1991</v>
+        <v>1997</v>
       </c>
       <c r="M429">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="N429" t="inlineStr">
         <is>
@@ -82874,7 +82867,7 @@
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>Ensino primário</t>
+          <t>12a classe</t>
         </is>
       </c>
       <c r="P429" t="inlineStr">
@@ -82883,13 +82876,33 @@
         </is>
       </c>
       <c r="Q429">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R429" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>05/2020</t>
+        </is>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>MUIDUMBE</t>
+        </is>
+      </c>
+      <c r="V429" t="inlineStr">
+        <is>
+          <t>Sozinha/o com seu AF da sua origem</t>
+        </is>
+      </c>
+      <c r="W429" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="X429" t="inlineStr">
         <is>
           <t>Não</t>
@@ -82917,7 +82930,7 @@
       </c>
       <c r="AF429" t="inlineStr">
         <is>
-          <t>MATERIAL DE USO CASEIRO</t>
+          <t>PRODUTOS ALIMENTAR, VESTUARIO E EQUIPAMENTOS DA COZINHAR</t>
         </is>
       </c>
       <c r="AG429">
@@ -82925,11 +82938,8 @@
       </c>
       <c r="AH429" t="inlineStr">
         <is>
-          <t>MATERIAL DE HIGIENE</t>
-        </is>
-      </c>
-      <c r="AI429">
-        <v>2</v>
+          <t>##N/A##</t>
+        </is>
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
@@ -82953,6 +82963,16 @@
       </c>
       <c r="BA429" t="inlineStr">
         <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BB429" t="inlineStr">
+        <is>
+          <t>864-811-102</t>
+        </is>
+      </c>
+      <c r="BC429" t="inlineStr">
+        <is>
           <t>Não</t>
         </is>
       </c>
@@ -82963,12 +82983,12 @@
       </c>
       <c r="BF429" t="inlineStr">
         <is>
-          <t>Mãe/pai</t>
+          <t>Irmã/o</t>
         </is>
       </c>
       <c r="BG429" t="inlineStr">
         <is>
-          <t>871-740-714</t>
+          <t>853-445-534</t>
         </is>
       </c>
       <c r="BH429" t="inlineStr">
@@ -82978,22 +82998,22 @@
       </c>
       <c r="BK429" t="inlineStr">
         <is>
-          <t>Número alternativo</t>
+          <t>Número proprio</t>
         </is>
       </c>
       <c r="BL429" t="inlineStr">
         <is>
-          <t>Familia acolhedora</t>
+          <t>Deslocado</t>
         </is>
       </c>
       <c r="BM429" t="inlineStr">
         <is>
-          <t>Acolhedora</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="BO429" t="inlineStr">
         <is>
-          <t>PRJ_0376</t>
+          <t>PRJ_0520</t>
         </is>
       </c>
     </row>
@@ -83005,7 +83025,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>FAUSTINO BERNARDINO JUMATANO ROMAO</t>
+          <t>EUGENIO ANTONIO</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -83020,7 +83040,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -83040,12 +83060,12 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>09077A-01/424</t>
+          <t>092216-14052341213(090775-03/135)</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>VILA-SEDE</t>
+          <t>VILA SEDE</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
@@ -83054,24 +83074,32 @@
         </is>
       </c>
       <c r="L430">
-        <v>2004</v>
+        <v>1991</v>
       </c>
       <c r="M430">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="N430" t="inlineStr">
         <is>
-          <t>Solteria/o</t>
+          <t>Casada/o</t>
         </is>
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t>10a classe</t>
+          <t>Ensino primário</t>
         </is>
       </c>
       <c r="P430" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q430">
+        <v>4</v>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
       <c r="X430" t="inlineStr">
@@ -83101,7 +83129,7 @@
       </c>
       <c r="AF430" t="inlineStr">
         <is>
-          <t>RECEBI BALDES E MANTAS DA VISAO MUNDIAL</t>
+          <t>MATERIAL DE USO CASEIRO</t>
         </is>
       </c>
       <c r="AG430">
@@ -83109,69 +83137,34 @@
       </c>
       <c r="AH430" t="inlineStr">
         <is>
+          <t>MATERIAL DE HIGIENE</t>
+        </is>
+      </c>
+      <c r="AI430">
+        <v>2</v>
+      </c>
+      <c r="AJ430" t="inlineStr">
+        <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AJ430" t="inlineStr">
+      <c r="AL430" t="inlineStr">
         <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AL430" t="inlineStr">
+      <c r="AN430" t="inlineStr">
         <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AN430" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
       <c r="AP430" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AQ430" t="inlineStr">
-        <is>
-          <t>RECEBI MATERIAIS PARA MACHAMBAS (CATANA,  SEMENTES E ENCHADA).</t>
-        </is>
-      </c>
-      <c r="AR430">
-        <v>1</v>
-      </c>
-      <c r="AS430" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AU430" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AW430" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AY430" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BA430" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BB430" t="inlineStr">
-        <is>
-          <t>872-333-472</t>
-        </is>
-      </c>
-      <c r="BC430" t="inlineStr">
-        <is>
           <t>Não</t>
         </is>
       </c>
@@ -83182,12 +83175,12 @@
       </c>
       <c r="BF430" t="inlineStr">
         <is>
-          <t>Irmã/o</t>
+          <t>Mãe/pai</t>
         </is>
       </c>
       <c r="BG430" t="inlineStr">
         <is>
-          <t>864-654-667</t>
+          <t>871-740-714</t>
         </is>
       </c>
       <c r="BH430" t="inlineStr">
@@ -83197,7 +83190,7 @@
       </c>
       <c r="BK430" t="inlineStr">
         <is>
-          <t>Número proprio</t>
+          <t>Número alternativo</t>
         </is>
       </c>
       <c r="BL430" t="inlineStr">
@@ -83212,7 +83205,7 @@
       </c>
       <c r="BO430" t="inlineStr">
         <is>
-          <t>PRJ_0383</t>
+          <t>PRJ_0376</t>
         </is>
       </c>
     </row>
@@ -83224,7 +83217,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>FAUSTINO MIGUEL BULASSE</t>
+          <t>FAUSTINO BERNARDINO JUMATANO ROMAO</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -83239,7 +83232,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -83254,17 +83247,17 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>Cartão de Eleitor</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>021108871012Q</t>
+          <t>09077A-01/424</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>VILA SEDE</t>
+          <t>VILA-SEDE</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
@@ -83273,10 +83266,10 @@
         </is>
       </c>
       <c r="L431">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="M431">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N431" t="inlineStr">
         <is>
@@ -83285,7 +83278,7 @@
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t>12a classe</t>
+          <t>10a classe</t>
         </is>
       </c>
       <c r="P431" t="inlineStr">
@@ -83295,12 +83288,7 @@
       </c>
       <c r="X431" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Y431" t="inlineStr">
-        <is>
-          <t>COMERCIANTE</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="Z431" t="inlineStr">
@@ -83320,12 +83308,68 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AF431" t="inlineStr">
+        <is>
+          <t>RECEBI BALDES E MANTAS DA VISAO MUNDIAL</t>
+        </is>
+      </c>
+      <c r="AG431">
+        <v>1</v>
+      </c>
+      <c r="AH431" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AJ431" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AL431" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AN431" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="AP431" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AQ431" t="inlineStr">
+        <is>
+          <t>RECEBI MATERIAIS PARA MACHAMBAS (CATANA,  SEMENTES E ENCHADA).</t>
+        </is>
+      </c>
+      <c r="AR431">
+        <v>1</v>
+      </c>
+      <c r="AS431" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AU431" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AW431" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AY431" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="BA431" t="inlineStr">
@@ -83335,7 +83379,7 @@
       </c>
       <c r="BB431" t="inlineStr">
         <is>
-          <t>867-618-804</t>
+          <t>872-333-472</t>
         </is>
       </c>
       <c r="BC431" t="inlineStr">
@@ -83345,7 +83389,27 @@
       </c>
       <c r="BE431" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BF431" t="inlineStr">
+        <is>
+          <t>Irmã/o</t>
+        </is>
+      </c>
+      <c r="BG431" t="inlineStr">
+        <is>
+          <t>864-654-667</t>
+        </is>
+      </c>
+      <c r="BH431" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="BK431" t="inlineStr">
+        <is>
+          <t>Número proprio</t>
         </is>
       </c>
       <c r="BL431" t="inlineStr">
@@ -83360,7 +83424,7 @@
       </c>
       <c r="BO431" t="inlineStr">
         <is>
-          <t>PRJ_0384</t>
+          <t>PRJ_0383</t>
         </is>
       </c>
     </row>
@@ -83372,7 +83436,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>IBRAIMO CANDIDO JOAO</t>
+          <t>FAUSTINO MIGUEL BULASSE</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -83387,7 +83451,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -83407,7 +83471,7 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>031307316806F</t>
+          <t>021108871012Q</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
@@ -83421,14 +83485,14 @@
         </is>
       </c>
       <c r="L432">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="M432">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t>Casada/o</t>
+          <t>Solteria/o</t>
         </is>
       </c>
       <c r="O432" t="inlineStr">
@@ -83438,20 +83502,17 @@
       </c>
       <c r="P432" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q432">
-        <v>1</v>
-      </c>
-      <c r="R432" t="inlineStr">
-        <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="X432" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Y432" t="inlineStr">
+        <is>
+          <t>COMERCIANTE</t>
         </is>
       </c>
       <c r="Z432" t="inlineStr">
@@ -83461,12 +83522,7 @@
       </c>
       <c r="AA432" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AB432" t="inlineStr">
-        <is>
-          <t>PROJECTO CULIMA- FORMACAO SOBRE RECOLHA DE DADOS NA COMUNIDADE</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AC432" t="inlineStr">
@@ -83491,7 +83547,7 @@
       </c>
       <c r="BB432" t="inlineStr">
         <is>
-          <t>870-797-866</t>
+          <t>867-618-804</t>
         </is>
       </c>
       <c r="BC432" t="inlineStr">
@@ -83514,14 +83570,9 @@
           <t>Acolhedora</t>
         </is>
       </c>
-      <c r="BN432" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
       <c r="BO432" t="inlineStr">
         <is>
-          <t>PRJ_0397</t>
+          <t>PRJ_0384</t>
         </is>
       </c>
     </row>
@@ -83533,7 +83584,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>JUNIOR MOMADE USSENE</t>
+          <t>IBRAIMO CANDIDO JOAO</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -83548,7 +83599,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -83568,7 +83619,7 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>031308884305P</t>
+          <t>031307316806F</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
@@ -83582,14 +83633,14 @@
         </is>
       </c>
       <c r="L433">
-        <v>2006</v>
+        <v>1997</v>
       </c>
       <c r="M433">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="N433" t="inlineStr">
         <is>
-          <t>Solteria/o</t>
+          <t>Casada/o</t>
         </is>
       </c>
       <c r="O433" t="inlineStr">
@@ -83599,25 +83650,13 @@
       </c>
       <c r="P433" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="T433" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U433" t="inlineStr">
-        <is>
-          <t>MUIDUMBE</t>
-        </is>
-      </c>
-      <c r="V433" t="inlineStr">
-        <is>
-          <t>Sozinha/o com seu AF da sua origem</t>
-        </is>
-      </c>
-      <c r="W433" t="inlineStr">
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q433">
+        <v>1</v>
+      </c>
+      <c r="R433" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -83634,7 +83673,12 @@
       </c>
       <c r="AA433" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AB433" t="inlineStr">
+        <is>
+          <t>PROJECTO CULIMA- FORMACAO SOBRE RECOLHA DE DADOS NA COMUNIDADE</t>
         </is>
       </c>
       <c r="AC433" t="inlineStr">
@@ -83644,35 +83688,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AF433" t="inlineStr">
-        <is>
-          <t>PRODUTOS ALIMENTARES</t>
-        </is>
-      </c>
-      <c r="AG433">
-        <v>1</v>
-      </c>
-      <c r="AH433" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AJ433" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AL433" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AN433" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AP433" t="inlineStr">
@@ -83687,7 +83703,7 @@
       </c>
       <c r="BB433" t="inlineStr">
         <is>
-          <t>867-568-971</t>
+          <t>870-797-866</t>
         </is>
       </c>
       <c r="BC433" t="inlineStr">
@@ -83697,42 +83713,27 @@
       </c>
       <c r="BE433" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BF433" t="inlineStr">
-        <is>
-          <t>Mãe/pai</t>
-        </is>
-      </c>
-      <c r="BG433" t="inlineStr">
-        <is>
-          <t>867-803-973</t>
-        </is>
-      </c>
-      <c r="BH433" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="BK433" t="inlineStr">
-        <is>
-          <t>Número proprio</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BL433" t="inlineStr">
         <is>
-          <t>Deslocado</t>
+          <t>Familia acolhedora</t>
         </is>
       </c>
       <c r="BM433" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Acolhedora</t>
+        </is>
+      </c>
+      <c r="BN433" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="BO433" t="inlineStr">
         <is>
-          <t>PRJ_0519</t>
+          <t>PRJ_0397</t>
         </is>
       </c>
     </row>
@@ -83744,7 +83745,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>LEONARDO DE KAMUHA JOSE TOMAS</t>
+          <t>JUNIOR MOMADE USSENE</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -83759,7 +83760,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -83779,7 +83780,7 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>031308873524P</t>
+          <t>031308884305P</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -83793,7 +83794,7 @@
         </is>
       </c>
       <c r="L434">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="M434">
         <v>19</v>
@@ -83805,7 +83806,7 @@
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t>9a classe</t>
+          <t>12a classe</t>
         </is>
       </c>
       <c r="P434" t="inlineStr">
@@ -83815,7 +83816,7 @@
       </c>
       <c r="T434" t="inlineStr">
         <is>
-          <t>06/2020</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="U434" t="inlineStr">
@@ -83825,7 +83826,7 @@
       </c>
       <c r="V434" t="inlineStr">
         <is>
-          <t>Familia acolhedora</t>
+          <t>Sozinha/o com seu AF da sua origem</t>
         </is>
       </c>
       <c r="W434" t="inlineStr">
@@ -83835,17 +83836,12 @@
       </c>
       <c r="X434" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Y434" t="inlineStr">
-        <is>
-          <t>VENDA DE FROZY E AGUA</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="Z434" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AA434" t="inlineStr">
@@ -83873,19 +83869,13 @@
       </c>
       <c r="AH434" t="inlineStr">
         <is>
-          <t>MATERIAL PARA USO DOMÉSTICO</t>
-        </is>
-      </c>
-      <c r="AI434">
-        <v>2</v>
+          <t>##N/A##</t>
+        </is>
       </c>
       <c r="AJ434" t="inlineStr">
         <is>
-          <t>COBERTORES</t>
-        </is>
-      </c>
-      <c r="AK434">
-        <v>3</v>
+          <t>##N/A##</t>
+        </is>
       </c>
       <c r="AL434" t="inlineStr">
         <is>
@@ -83899,35 +83889,7 @@
       </c>
       <c r="AP434" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AQ434" t="inlineStr">
-        <is>
-          <t>INSUMOS AGRICOLA</t>
-        </is>
-      </c>
-      <c r="AR434">
-        <v>1</v>
-      </c>
-      <c r="AS434" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AU434" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AW434" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AY434" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BA434" t="inlineStr">
@@ -83937,7 +83899,7 @@
       </c>
       <c r="BB434" t="inlineStr">
         <is>
-          <t>860-422-526</t>
+          <t>867-568-971</t>
         </is>
       </c>
       <c r="BC434" t="inlineStr">
@@ -83957,27 +83919,17 @@
       </c>
       <c r="BG434" t="inlineStr">
         <is>
-          <t>861-668-633</t>
+          <t>867-803-973</t>
         </is>
       </c>
       <c r="BH434" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BI434" t="inlineStr">
-        <is>
-          <t>Irmã/o</t>
-        </is>
-      </c>
-      <c r="BJ434" t="inlineStr">
-        <is>
-          <t>867-565-225</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BK434" t="inlineStr">
         <is>
-          <t>Número alternativo</t>
+          <t>Número proprio</t>
         </is>
       </c>
       <c r="BL434" t="inlineStr">
@@ -83990,14 +83942,9 @@
           <t>IDP</t>
         </is>
       </c>
-      <c r="BN434" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
       <c r="BO434" t="inlineStr">
         <is>
-          <t>PRJ_0493</t>
+          <t>PRJ_0519</t>
         </is>
       </c>
     </row>
@@ -84009,7 +83956,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>MARIA AGOSTINHO ANTONIO</t>
+          <t>LEONARDO DE KAMUHA JOSE TOMAS</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -84024,7 +83971,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -84039,12 +83986,12 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Cartão de Eleitor</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>092120-25042338660 (090542-01/388)</t>
+          <t>031308873524P</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
@@ -84058,30 +84005,42 @@
         </is>
       </c>
       <c r="L435">
-        <v>1999</v>
+        <v>2007</v>
       </c>
       <c r="M435">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N435" t="inlineStr">
         <is>
-          <t>Casada/o</t>
+          <t>Solteria/o</t>
         </is>
       </c>
       <c r="O435" t="inlineStr">
         <is>
-          <t>12a classe</t>
+          <t>9a classe</t>
         </is>
       </c>
       <c r="P435" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q435">
-        <v>1</v>
-      </c>
-      <c r="R435" t="inlineStr">
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>06/2020</t>
+        </is>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>MUIDUMBE</t>
+        </is>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>Familia acolhedora</t>
+        </is>
+      </c>
+      <c r="W435" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -84093,12 +84052,12 @@
       </c>
       <c r="Y435" t="inlineStr">
         <is>
-          <t>VENDA DE CAPULANAS</t>
+          <t>VENDA DE FROZY E AGUA</t>
         </is>
       </c>
       <c r="Z435" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="AA435" t="inlineStr">
@@ -84118,7 +84077,7 @@
       </c>
       <c r="AF435" t="inlineStr">
         <is>
-          <t>RECEBI PANELAS E BALDES.</t>
+          <t>PRODUTOS ALIMENTARES</t>
         </is>
       </c>
       <c r="AG435">
@@ -84126,27 +84085,61 @@
       </c>
       <c r="AH435" t="inlineStr">
         <is>
+          <t>MATERIAL PARA USO DOMÉSTICO</t>
+        </is>
+      </c>
+      <c r="AI435">
+        <v>2</v>
+      </c>
+      <c r="AJ435" t="inlineStr">
+        <is>
+          <t>COBERTORES</t>
+        </is>
+      </c>
+      <c r="AK435">
+        <v>3</v>
+      </c>
+      <c r="AL435" t="inlineStr">
+        <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AJ435" t="inlineStr">
+      <c r="AN435" t="inlineStr">
         <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AL435" t="inlineStr">
+      <c r="AP435" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AQ435" t="inlineStr">
+        <is>
+          <t>INSUMOS AGRICOLA</t>
+        </is>
+      </c>
+      <c r="AR435">
+        <v>1</v>
+      </c>
+      <c r="AS435" t="inlineStr">
         <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AN435" t="inlineStr">
+      <c r="AU435" t="inlineStr">
         <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AP435" t="inlineStr">
-        <is>
-          <t>Não</t>
+      <c r="AW435" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AY435" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="BA435" t="inlineStr">
@@ -84156,7 +84149,7 @@
       </c>
       <c r="BB435" t="inlineStr">
         <is>
-          <t>866-305-318</t>
+          <t>860-422-526</t>
         </is>
       </c>
       <c r="BC435" t="inlineStr">
@@ -84176,32 +84169,47 @@
       </c>
       <c r="BG435" t="inlineStr">
         <is>
-          <t>872-528-789</t>
+          <t>861-668-633</t>
         </is>
       </c>
       <c r="BH435" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BI435" t="inlineStr">
+        <is>
+          <t>Irmã/o</t>
+        </is>
+      </c>
+      <c r="BJ435" t="inlineStr">
+        <is>
+          <t>867-565-225</t>
         </is>
       </c>
       <c r="BK435" t="inlineStr">
         <is>
-          <t>Número proprio</t>
+          <t>Número alternativo</t>
         </is>
       </c>
       <c r="BL435" t="inlineStr">
         <is>
-          <t>Familia acolhedora</t>
+          <t>Deslocado</t>
         </is>
       </c>
       <c r="BM435" t="inlineStr">
         <is>
-          <t>Acolhedora</t>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="BN435" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="BO435" t="inlineStr">
         <is>
-          <t>PRJ_0378</t>
+          <t>PRJ_0493</t>
         </is>
       </c>
     </row>
@@ -84213,7 +84221,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>MARIA DE FATIMA CRISTOVAO ALFREDO</t>
+          <t>MARIA AGOSTINHO ANTONIO</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -84228,7 +84236,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -84243,12 +84251,12 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>Cartão de Eleitor</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>03130886991C</t>
+          <t>092120-25042338660 (090542-01/388)</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -84258,58 +84266,51 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="L436">
-        <v>2004</v>
+        <v>1999</v>
       </c>
       <c r="M436">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N436" t="inlineStr">
         <is>
-          <t>Solteria/o</t>
+          <t>Casada/o</t>
         </is>
       </c>
       <c r="O436" t="inlineStr">
         <is>
-          <t>Ensino técnico médio</t>
+          <t>12a classe</t>
         </is>
       </c>
       <c r="P436" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="T436" t="inlineStr">
-        <is>
-          <t>06/2019</t>
-        </is>
-      </c>
-      <c r="U436" t="inlineStr">
-        <is>
-          <t>MUIDUMBE</t>
-        </is>
-      </c>
-      <c r="V436" t="inlineStr">
-        <is>
-          <t>Familia acolhedora</t>
-        </is>
-      </c>
-      <c r="W436" t="inlineStr">
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q436">
+        <v>1</v>
+      </c>
+      <c r="R436" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="X436" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Y436" t="inlineStr">
+        <is>
+          <t>VENDA DE CAPULANAS</t>
         </is>
       </c>
       <c r="Z436" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AA436" t="inlineStr">
@@ -84329,7 +84330,7 @@
       </c>
       <c r="AF436" t="inlineStr">
         <is>
-          <t>MATERIAL PARA USO DOMÉSTICO</t>
+          <t>RECEBI PANELAS E BALDES.</t>
         </is>
       </c>
       <c r="AG436">
@@ -84357,38 +84358,7 @@
       </c>
       <c r="AP436" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AQ436" t="inlineStr">
-        <is>
-          <t>INSUMOS AGRICOLA</t>
-        </is>
-      </c>
-      <c r="AR436">
-        <v>1</v>
-      </c>
-      <c r="AS436" t="inlineStr">
-        <is>
-          <t>MATERIAL PARA NEGOCIO (TRIGO, OLEO,PANELAS)</t>
-        </is>
-      </c>
-      <c r="AT436">
-        <v>2</v>
-      </c>
-      <c r="AU436" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AW436" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AY436" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BA436" t="inlineStr">
@@ -84398,17 +84368,12 @@
       </c>
       <c r="BB436" t="inlineStr">
         <is>
-          <t>861-466-222</t>
+          <t>866-305-318</t>
         </is>
       </c>
       <c r="BC436" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BD436" t="inlineStr">
-        <is>
-          <t>841-751-112</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BE436" t="inlineStr">
@@ -84418,27 +84383,17 @@
       </c>
       <c r="BF436" t="inlineStr">
         <is>
-          <t>Tio/a</t>
+          <t>Mãe/pai</t>
         </is>
       </c>
       <c r="BG436" t="inlineStr">
         <is>
-          <t>872-498-991</t>
+          <t>872-528-789</t>
         </is>
       </c>
       <c r="BH436" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BI436" t="inlineStr">
-        <is>
-          <t>Tio/a</t>
-        </is>
-      </c>
-      <c r="BJ436" t="inlineStr">
-        <is>
-          <t>870-502-144</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BK436" t="inlineStr">
@@ -84448,22 +84403,17 @@
       </c>
       <c r="BL436" t="inlineStr">
         <is>
-          <t>Deslocado</t>
+          <t>Familia acolhedora</t>
         </is>
       </c>
       <c r="BM436" t="inlineStr">
         <is>
-          <t>IDP</t>
-        </is>
-      </c>
-      <c r="BN436" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
+          <t>Acolhedora</t>
         </is>
       </c>
       <c r="BO436" t="inlineStr">
         <is>
-          <t>PRJ_0516</t>
+          <t>PRJ_0378</t>
         </is>
       </c>
     </row>
@@ -84475,7 +84425,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>MARIA FREDERICO JOAQUIM</t>
+          <t>MARIA DE FATIMA CRISTOVAO ALFREDO</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -84490,7 +84440,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -84505,12 +84455,12 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Cartão de Eleitor</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>101749-29032430444(100598-06/550)</t>
+          <t>03130886991C</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
@@ -84524,47 +84474,39 @@
         </is>
       </c>
       <c r="L437">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="M437">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N437" t="inlineStr">
         <is>
-          <t>Casada/o</t>
+          <t>Solteria/o</t>
         </is>
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>8a classe</t>
+          <t>Ensino técnico médio</t>
         </is>
       </c>
       <c r="P437" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q437">
-        <v>3</v>
-      </c>
-      <c r="R437" t="inlineStr">
-        <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T437" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>06/2019</t>
         </is>
       </c>
       <c r="U437" t="inlineStr">
         <is>
-          <t>MOCIMBOA DA PRAIA</t>
+          <t>MUIDUMBE</t>
         </is>
       </c>
       <c r="V437" t="inlineStr">
         <is>
-          <t>Sozinha/o com seu AF da sua origem</t>
+          <t>Familia acolhedora</t>
         </is>
       </c>
       <c r="W437" t="inlineStr">
@@ -84579,7 +84521,7 @@
       </c>
       <c r="Z437" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="AA437" t="inlineStr">
@@ -84599,7 +84541,7 @@
       </c>
       <c r="AF437" t="inlineStr">
         <is>
-          <t>PRODUTOS ALIMENTARES E DOMESTICOS</t>
+          <t>MATERIAL PARA USO DOMÉSTICO</t>
         </is>
       </c>
       <c r="AG437">
@@ -84632,7 +84574,7 @@
       </c>
       <c r="AQ437" t="inlineStr">
         <is>
-          <t>INSUMOS AGRICOLAS (SEMENTES), MATERIAL DA MACHAMBA (ENXADA, CATANA)</t>
+          <t>INSUMOS AGRICOLA</t>
         </is>
       </c>
       <c r="AR437">
@@ -84640,24 +84582,27 @@
       </c>
       <c r="AS437" t="inlineStr">
         <is>
+          <t>MATERIAL PARA NEGOCIO (TRIGO, OLEO,PANELAS)</t>
+        </is>
+      </c>
+      <c r="AT437">
+        <v>2</v>
+      </c>
+      <c r="AU437" t="inlineStr">
+        <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AU437" t="inlineStr">
+      <c r="AW437" t="inlineStr">
         <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AW437" t="inlineStr">
+      <c r="AY437" t="inlineStr">
         <is>
           <t>##N/A##</t>
         </is>
       </c>
-      <c r="AY437" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
       <c r="BA437" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -84665,12 +84610,17 @@
       </c>
       <c r="BB437" t="inlineStr">
         <is>
-          <t>847-547-919</t>
+          <t>861-466-222</t>
         </is>
       </c>
       <c r="BC437" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BD437" t="inlineStr">
+        <is>
+          <t>841-751-112</t>
         </is>
       </c>
       <c r="BE437" t="inlineStr">
@@ -84680,17 +84630,27 @@
       </c>
       <c r="BF437" t="inlineStr">
         <is>
-          <t>Esposo/a</t>
+          <t>Tio/a</t>
         </is>
       </c>
       <c r="BG437" t="inlineStr">
         <is>
-          <t>842-692-349</t>
+          <t>872-498-991</t>
         </is>
       </c>
       <c r="BH437" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BI437" t="inlineStr">
+        <is>
+          <t>Tio/a</t>
+        </is>
+      </c>
+      <c r="BJ437" t="inlineStr">
+        <is>
+          <t>870-502-144</t>
         </is>
       </c>
       <c r="BK437" t="inlineStr">
@@ -84708,9 +84668,14 @@
           <t>IDP</t>
         </is>
       </c>
+      <c r="BN437" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
       <c r="BO437" t="inlineStr">
         <is>
-          <t>PRJ_0528</t>
+          <t>PRJ_0516</t>
         </is>
       </c>
     </row>
@@ -84722,7 +84687,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>MARIAMO NURO</t>
+          <t>MARIA FREDERICO JOAQUIM</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -84737,7 +84702,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -84752,12 +84717,12 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>Cartão de Eleitor</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>020908900178B</t>
+          <t>101749-29032430444(100598-06/550)</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
@@ -84771,29 +84736,37 @@
         </is>
       </c>
       <c r="L438">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="M438">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N438" t="inlineStr">
         <is>
-          <t>Solteria/o</t>
+          <t>Casada/o</t>
         </is>
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>9a classe</t>
+          <t>8a classe</t>
         </is>
       </c>
       <c r="P438" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q438">
+        <v>3</v>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T438" t="inlineStr">
         <is>
-          <t>03/2020</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="U438" t="inlineStr">
@@ -84803,12 +84776,12 @@
       </c>
       <c r="V438" t="inlineStr">
         <is>
-          <t>Familia acolhedora</t>
+          <t>Sozinha/o com seu AF da sua origem</t>
         </is>
       </c>
       <c r="W438" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="X438" t="inlineStr">
@@ -84838,7 +84811,7 @@
       </c>
       <c r="AF438" t="inlineStr">
         <is>
-          <t>RECEBI MATERIAL DE HIGIENE PESSOAL E PRODUTOS ALIMENTARES</t>
+          <t>PRODUTOS ALIMENTARES E DOMESTICOS</t>
         </is>
       </c>
       <c r="AG438">
@@ -84866,11 +84839,49 @@
       </c>
       <c r="AP438" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AQ438" t="inlineStr">
+        <is>
+          <t>INSUMOS AGRICOLAS (SEMENTES), MATERIAL DA MACHAMBA (ENXADA, CATANA)</t>
+        </is>
+      </c>
+      <c r="AR438">
+        <v>1</v>
+      </c>
+      <c r="AS438" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AU438" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AW438" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AY438" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="BA438" t="inlineStr">
         <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BB438" t="inlineStr">
+        <is>
+          <t>847-547-919</t>
+        </is>
+      </c>
+      <c r="BC438" t="inlineStr">
+        <is>
           <t>Não</t>
         </is>
       </c>
@@ -84881,32 +84892,22 @@
       </c>
       <c r="BF438" t="inlineStr">
         <is>
-          <t>Mãe/pai</t>
+          <t>Esposo/a</t>
         </is>
       </c>
       <c r="BG438" t="inlineStr">
         <is>
-          <t>862-964-870</t>
+          <t>842-692-349</t>
         </is>
       </c>
       <c r="BH438" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BI438" t="inlineStr">
-        <is>
-          <t>Tio/a</t>
-        </is>
-      </c>
-      <c r="BJ438" t="inlineStr">
-        <is>
-          <t>857-106-331</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BK438" t="inlineStr">
         <is>
-          <t>Número alternativo</t>
+          <t>Número proprio</t>
         </is>
       </c>
       <c r="BL438" t="inlineStr">
@@ -84921,7 +84922,7 @@
       </c>
       <c r="BO438" t="inlineStr">
         <is>
-          <t>PRJ_0513</t>
+          <t>PRJ_0528</t>
         </is>
       </c>
     </row>
@@ -84933,7 +84934,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>MARTA JOHN MANUEL</t>
+          <t>MARIAMO NURO</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -84948,7 +84949,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -84968,7 +84969,7 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>020106761124D</t>
+          <t>020908900178B</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
@@ -84982,47 +84983,39 @@
         </is>
       </c>
       <c r="L439">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="M439">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t>Casada/o</t>
+          <t>Solteria/o</t>
         </is>
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>12a classe</t>
+          <t>9a classe</t>
         </is>
       </c>
       <c r="P439" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q439">
-        <v>2</v>
-      </c>
-      <c r="R439" t="inlineStr">
-        <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T439" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>03/2020</t>
         </is>
       </c>
       <c r="U439" t="inlineStr">
         <is>
-          <t>MUIDUMBI</t>
+          <t>MOCIMBOA DA PRAIA</t>
         </is>
       </c>
       <c r="V439" t="inlineStr">
         <is>
-          <t>Sozinha/o com seu AF da sua origem</t>
+          <t>Familia acolhedora</t>
         </is>
       </c>
       <c r="W439" t="inlineStr">
@@ -85032,12 +85025,7 @@
       </c>
       <c r="X439" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Y439" t="inlineStr">
-        <is>
-          <t>VENDA DE PEIXES FRESCOS.</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="Z439" t="inlineStr">
@@ -85062,7 +85050,7 @@
       </c>
       <c r="AF439" t="inlineStr">
         <is>
-          <t>RECEBI PRODUTOS ALIMENTARES DA PMA</t>
+          <t>RECEBI MATERIAL DE HIGIENE PESSOAL E PRODUTOS ALIMENTARES</t>
         </is>
       </c>
       <c r="AG439">
@@ -85095,16 +85083,6 @@
       </c>
       <c r="BA439" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BB439" t="inlineStr">
-        <is>
-          <t>871-903-730</t>
-        </is>
-      </c>
-      <c r="BC439" t="inlineStr">
-        <is>
           <t>Não</t>
         </is>
       </c>
@@ -85120,17 +85098,27 @@
       </c>
       <c r="BG439" t="inlineStr">
         <is>
-          <t>872-200-376</t>
+          <t>862-964-870</t>
         </is>
       </c>
       <c r="BH439" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BI439" t="inlineStr">
+        <is>
+          <t>Tio/a</t>
+        </is>
+      </c>
+      <c r="BJ439" t="inlineStr">
+        <is>
+          <t>857-106-331</t>
         </is>
       </c>
       <c r="BK439" t="inlineStr">
         <is>
-          <t>Número proprio</t>
+          <t>Número alternativo</t>
         </is>
       </c>
       <c r="BL439" t="inlineStr">
@@ -85145,7 +85133,7 @@
       </c>
       <c r="BO439" t="inlineStr">
         <is>
-          <t>PRJ_0529</t>
+          <t>PRJ_0513</t>
         </is>
       </c>
     </row>
@@ -85157,7 +85145,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>MATEUS FERNANDO CAMILO</t>
+          <t>MARTA JOHN MANUEL</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -85172,7 +85160,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
@@ -85187,12 +85175,12 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Cartão de Eleitor</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>092216-25032478464(090774-02/740)</t>
+          <t>020106761124D</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -85202,14 +85190,14 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="L440">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="M440">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N440" t="inlineStr">
         <is>
@@ -85218,7 +85206,7 @@
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t>7a classe</t>
+          <t>12a classe</t>
         </is>
       </c>
       <c r="P440" t="inlineStr">
@@ -85227,7 +85215,7 @@
         </is>
       </c>
       <c r="Q440">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R440" t="inlineStr">
         <is>
@@ -85236,27 +85224,32 @@
       </c>
       <c r="T440" t="inlineStr">
         <is>
-          <t>04/2020</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="U440" t="inlineStr">
         <is>
-          <t>MOCIMBOA DA PRAIA</t>
+          <t>MUIDUMBI</t>
         </is>
       </c>
       <c r="V440" t="inlineStr">
         <is>
-          <t>Familia acolhedora</t>
+          <t>Sozinha/o com seu AF da sua origem</t>
         </is>
       </c>
       <c r="W440" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="X440" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Y440" t="inlineStr">
+        <is>
+          <t>VENDA DE PEIXES FRESCOS.</t>
         </is>
       </c>
       <c r="Z440" t="inlineStr">
@@ -85281,7 +85274,7 @@
       </c>
       <c r="AF440" t="inlineStr">
         <is>
-          <t>PRODUTOS ALIMENTARES E  DOMESTICOS</t>
+          <t>RECEBI PRODUTOS ALIMENTARES DA PMA</t>
         </is>
       </c>
       <c r="AG440">
@@ -85319,17 +85312,12 @@
       </c>
       <c r="BB440" t="inlineStr">
         <is>
-          <t>866-108-695</t>
+          <t>871-903-730</t>
         </is>
       </c>
       <c r="BC440" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BD440" t="inlineStr">
-        <is>
-          <t>849-563-875</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BE440" t="inlineStr">
@@ -85339,12 +85327,12 @@
       </c>
       <c r="BF440" t="inlineStr">
         <is>
-          <t>Irmã/o</t>
+          <t>Mãe/pai</t>
         </is>
       </c>
       <c r="BG440" t="inlineStr">
         <is>
-          <t>864-124-480</t>
+          <t>872-200-376</t>
         </is>
       </c>
       <c r="BH440" t="inlineStr">
@@ -85369,7 +85357,7 @@
       </c>
       <c r="BO440" t="inlineStr">
         <is>
-          <t>PRJ_0506</t>
+          <t>PRJ_0529</t>
         </is>
       </c>
     </row>
@@ -85381,7 +85369,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>NANDO MARUFO CHANDE</t>
+          <t>MATEUS FERNANDO CAMILO</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -85396,7 +85384,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -85416,7 +85404,7 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>090504-24042431896</t>
+          <t>092216-25032478464(090774-02/740)</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -85430,24 +85418,52 @@
         </is>
       </c>
       <c r="L441">
-        <v>2006</v>
+        <v>1995</v>
       </c>
       <c r="M441">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="N441" t="inlineStr">
         <is>
-          <t>Solteria/o</t>
+          <t>Casada/o</t>
         </is>
       </c>
       <c r="O441" t="inlineStr">
         <is>
-          <t>10a classe</t>
+          <t>7a classe</t>
         </is>
       </c>
       <c r="P441" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q441">
+        <v>1</v>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>04/2020</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>MOCIMBOA DA PRAIA</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>Familia acolhedora</t>
+        </is>
+      </c>
+      <c r="W441" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
       <c r="X441" t="inlineStr">
@@ -85477,7 +85493,7 @@
       </c>
       <c r="AF441" t="inlineStr">
         <is>
-          <t>RECEBI MATERIAL DOMESTICO.</t>
+          <t>PRODUTOS ALIMENTARES E  DOMESTICOS</t>
         </is>
       </c>
       <c r="AG441">
@@ -85510,7 +85526,22 @@
       </c>
       <c r="BA441" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BB441" t="inlineStr">
+        <is>
+          <t>866-108-695</t>
+        </is>
+      </c>
+      <c r="BC441" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BD441" t="inlineStr">
+        <is>
+          <t>849-563-875</t>
         </is>
       </c>
       <c r="BE441" t="inlineStr">
@@ -85520,12 +85551,12 @@
       </c>
       <c r="BF441" t="inlineStr">
         <is>
-          <t>Mãe/pai</t>
+          <t>Irmã/o</t>
         </is>
       </c>
       <c r="BG441" t="inlineStr">
         <is>
-          <t>866-079-603</t>
+          <t>864-124-480</t>
         </is>
       </c>
       <c r="BH441" t="inlineStr">
@@ -85535,22 +85566,22 @@
       </c>
       <c r="BK441" t="inlineStr">
         <is>
-          <t>Número alternativo</t>
+          <t>Número proprio</t>
         </is>
       </c>
       <c r="BL441" t="inlineStr">
         <is>
-          <t>Familia acolhedora</t>
+          <t>Deslocado</t>
         </is>
       </c>
       <c r="BM441" t="inlineStr">
         <is>
-          <t>Acolhedora</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="BO441" t="inlineStr">
         <is>
-          <t>PRJ_0382</t>
+          <t>PRJ_0506</t>
         </is>
       </c>
     </row>
@@ -85562,7 +85593,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>NELINHO CARLITOS VICENTE</t>
+          <t>NANDO MARUFO CHANDE</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -85577,7 +85608,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -85592,12 +85623,12 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>Cartão de Eleitor</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>0313038868205M</t>
+          <t>090504-24042431896</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
@@ -85611,14 +85642,14 @@
         </is>
       </c>
       <c r="L442">
-        <v>1999</v>
+        <v>2006</v>
       </c>
       <c r="M442">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N442" t="inlineStr">
         <is>
-          <t>Casada/o</t>
+          <t>Solteria/o</t>
         </is>
       </c>
       <c r="O442" t="inlineStr">
@@ -85628,45 +85659,12 @@
       </c>
       <c r="P442" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q442">
-        <v>1</v>
-      </c>
-      <c r="R442" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="T442" t="inlineStr">
-        <is>
-          <t>12/2019</t>
-        </is>
-      </c>
-      <c r="U442" t="inlineStr">
-        <is>
-          <t>MOCIMBOA DA PRAIA</t>
-        </is>
-      </c>
-      <c r="V442" t="inlineStr">
-        <is>
-          <t>Sozinha/o com seu AF da sua origem</t>
-        </is>
-      </c>
-      <c r="W442" t="inlineStr">
-        <is>
           <t>Não</t>
         </is>
       </c>
       <c r="X442" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Y442" t="inlineStr">
-        <is>
-          <t>COMERCIANTE</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="Z442" t="inlineStr">
@@ -85691,7 +85689,7 @@
       </c>
       <c r="AF442" t="inlineStr">
         <is>
-          <t>RECEBI PRODUTOS ALIMENTARES DA PMA</t>
+          <t>RECEBI MATERIAL DOMESTICO.</t>
         </is>
       </c>
       <c r="AG442">
@@ -85719,49 +85717,11 @@
       </c>
       <c r="AP442" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AQ442" t="inlineStr">
-        <is>
-          <t>RECRBI MATERIAS PRIMAS PARA FAZER MEU NEGOCI(TRIGO, FAVO DE OVO).</t>
-        </is>
-      </c>
-      <c r="AR442">
-        <v>1</v>
-      </c>
-      <c r="AS442" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AU442" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AW442" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AY442" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BA442" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BB442" t="inlineStr">
-        <is>
-          <t>865-955-537</t>
-        </is>
-      </c>
-      <c r="BC442" t="inlineStr">
-        <is>
           <t>Não</t>
         </is>
       </c>
@@ -85772,12 +85732,12 @@
       </c>
       <c r="BF442" t="inlineStr">
         <is>
-          <t>Irmã/o</t>
+          <t>Mãe/pai</t>
         </is>
       </c>
       <c r="BG442" t="inlineStr">
         <is>
-          <t>871-355-537</t>
+          <t>866-079-603</t>
         </is>
       </c>
       <c r="BH442" t="inlineStr">
@@ -85787,22 +85747,22 @@
       </c>
       <c r="BK442" t="inlineStr">
         <is>
-          <t>Número proprio</t>
+          <t>Número alternativo</t>
         </is>
       </c>
       <c r="BL442" t="inlineStr">
         <is>
-          <t>Deslocado</t>
+          <t>Familia acolhedora</t>
         </is>
       </c>
       <c r="BM442" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Acolhedora</t>
         </is>
       </c>
       <c r="BO442" t="inlineStr">
         <is>
-          <t>PRJ_0531</t>
+          <t>PRJ_0382</t>
         </is>
       </c>
     </row>
@@ -85814,7 +85774,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>NELSON MUSSA CHALE CANITEA</t>
+          <t>NELINHO CARLITOS VICENTE</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -85829,7 +85789,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -85849,7 +85809,7 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>031308882572S</t>
+          <t>0313038868205M</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
@@ -85863,10 +85823,10 @@
         </is>
       </c>
       <c r="L443">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="M443">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N443" t="inlineStr">
         <is>
@@ -85875,7 +85835,7 @@
       </c>
       <c r="O443" t="inlineStr">
         <is>
-          <t>9a classe</t>
+          <t>10a classe</t>
         </is>
       </c>
       <c r="P443" t="inlineStr">
@@ -85884,16 +85844,41 @@
         </is>
       </c>
       <c r="Q443">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R443" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>12/2019</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>MOCIMBOA DA PRAIA</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>Sozinha/o com seu AF da sua origem</t>
+        </is>
+      </c>
+      <c r="W443" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="X443" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Y443" t="inlineStr">
+        <is>
+          <t>COMERCIANTE</t>
         </is>
       </c>
       <c r="Z443" t="inlineStr">
@@ -85913,12 +85898,68 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AF443" t="inlineStr">
+        <is>
+          <t>RECEBI PRODUTOS ALIMENTARES DA PMA</t>
+        </is>
+      </c>
+      <c r="AG443">
+        <v>1</v>
+      </c>
+      <c r="AH443" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AJ443" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AL443" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AN443" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="AP443" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AQ443" t="inlineStr">
+        <is>
+          <t>RECRBI MATERIAS PRIMAS PARA FAZER MEU NEGOCI(TRIGO, FAVO DE OVO).</t>
+        </is>
+      </c>
+      <c r="AR443">
+        <v>1</v>
+      </c>
+      <c r="AS443" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AU443" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AW443" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AY443" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="BA443" t="inlineStr">
@@ -85928,7 +85969,7 @@
       </c>
       <c r="BB443" t="inlineStr">
         <is>
-          <t>865-965-254</t>
+          <t>865-955-537</t>
         </is>
       </c>
       <c r="BC443" t="inlineStr">
@@ -85943,12 +85984,12 @@
       </c>
       <c r="BF443" t="inlineStr">
         <is>
-          <t>Esposo/a</t>
+          <t>Irmã/o</t>
         </is>
       </c>
       <c r="BG443" t="inlineStr">
         <is>
-          <t>871-883-301</t>
+          <t>871-355-537</t>
         </is>
       </c>
       <c r="BH443" t="inlineStr">
@@ -85963,17 +86004,17 @@
       </c>
       <c r="BL443" t="inlineStr">
         <is>
-          <t>Familia acolhedora</t>
+          <t>Deslocado</t>
         </is>
       </c>
       <c r="BM443" t="inlineStr">
         <is>
-          <t>Acolhedora</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="BO443" t="inlineStr">
         <is>
-          <t>PRJ_0395</t>
+          <t>PRJ_0531</t>
         </is>
       </c>
     </row>
@@ -85985,7 +86026,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>PINCHA DIONISIO</t>
+          <t>NELSON MUSSA CHALE CANITEA</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -86000,7 +86041,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -86015,12 +86056,12 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Cédula Pessoal</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>996940</t>
+          <t>031308882572S</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
@@ -86034,19 +86075,19 @@
         </is>
       </c>
       <c r="L444">
-        <v>2006</v>
+        <v>1996</v>
       </c>
       <c r="M444">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="N444" t="inlineStr">
         <is>
-          <t>União marital</t>
+          <t>Casada/o</t>
         </is>
       </c>
       <c r="O444" t="inlineStr">
         <is>
-          <t>8a classe</t>
+          <t>9a classe</t>
         </is>
       </c>
       <c r="P444" t="inlineStr">
@@ -86055,7 +86096,7 @@
         </is>
       </c>
       <c r="Q444">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R444" t="inlineStr">
         <is>
@@ -86064,12 +86105,7 @@
       </c>
       <c r="X444" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Y444" t="inlineStr">
-        <is>
-          <t>VENDA DE BOLINHOS</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="Z444" t="inlineStr">
@@ -86089,35 +86125,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AF444" t="inlineStr">
-        <is>
-          <t>RECEBI  PRODUTOS ALIMENTARES</t>
-        </is>
-      </c>
-      <c r="AG444">
-        <v>1</v>
-      </c>
-      <c r="AH444" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AJ444" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AL444" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AN444" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AP444" t="inlineStr">
@@ -86132,7 +86140,7 @@
       </c>
       <c r="BB444" t="inlineStr">
         <is>
-          <t>867-017-649</t>
+          <t>865-965-254</t>
         </is>
       </c>
       <c r="BC444" t="inlineStr">
@@ -86152,7 +86160,7 @@
       </c>
       <c r="BG444" t="inlineStr">
         <is>
-          <t>864-018-972</t>
+          <t>871-883-301</t>
         </is>
       </c>
       <c r="BH444" t="inlineStr">
@@ -86177,7 +86185,7 @@
       </c>
       <c r="BO444" t="inlineStr">
         <is>
-          <t>PRJ_0398</t>
+          <t>PRJ_0395</t>
         </is>
       </c>
     </row>
@@ -86189,7 +86197,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>RAIMUNDO JOSE CARLOS ASSANE</t>
+          <t>PINCHA DIONISIO</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -86204,7 +86212,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -86224,7 +86232,7 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>799037</t>
+          <t>996940</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
@@ -86238,49 +86246,42 @@
         </is>
       </c>
       <c r="L445">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="M445">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N445" t="inlineStr">
         <is>
-          <t>Solteria/o</t>
+          <t>União marital</t>
         </is>
       </c>
       <c r="O445" t="inlineStr">
         <is>
-          <t>7a classe</t>
+          <t>8a classe</t>
         </is>
       </c>
       <c r="P445" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="T445" t="inlineStr">
-        <is>
-          <t>10/2020</t>
-        </is>
-      </c>
-      <c r="U445" t="inlineStr">
-        <is>
-          <t>MUIDUMBI</t>
-        </is>
-      </c>
-      <c r="V445" t="inlineStr">
-        <is>
-          <t>Sozinha/o com seu AF da sua origem</t>
-        </is>
-      </c>
-      <c r="W445" t="inlineStr">
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q445">
+        <v>2</v>
+      </c>
+      <c r="R445" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="X445" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Y445" t="inlineStr">
+        <is>
+          <t>VENDA DE BOLINHOS</t>
         </is>
       </c>
       <c r="Z445" t="inlineStr">
@@ -86305,7 +86306,7 @@
       </c>
       <c r="AF445" t="inlineStr">
         <is>
-          <t>RECEBI KIT DOMESTICOS (BALDES, PRATOS, MANTAS)</t>
+          <t>RECEBI  PRODUTOS ALIMENTARES</t>
         </is>
       </c>
       <c r="AG445">
@@ -86338,6 +86339,16 @@
       </c>
       <c r="BA445" t="inlineStr">
         <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BB445" t="inlineStr">
+        <is>
+          <t>867-017-649</t>
+        </is>
+      </c>
+      <c r="BC445" t="inlineStr">
+        <is>
           <t>Não</t>
         </is>
       </c>
@@ -86348,52 +86359,37 @@
       </c>
       <c r="BF445" t="inlineStr">
         <is>
-          <t>Mãe/pai</t>
+          <t>Esposo/a</t>
         </is>
       </c>
       <c r="BG445" t="inlineStr">
         <is>
-          <t>876-314-127</t>
+          <t>864-018-972</t>
         </is>
       </c>
       <c r="BH445" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BI445" t="inlineStr">
-        <is>
-          <t>Mãe/pai</t>
-        </is>
-      </c>
-      <c r="BJ445" t="inlineStr">
-        <is>
-          <t>872-498-991</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BK445" t="inlineStr">
         <is>
-          <t>Número alternativo</t>
+          <t>Número proprio</t>
         </is>
       </c>
       <c r="BL445" t="inlineStr">
         <is>
-          <t>Deslocado</t>
+          <t>Familia acolhedora</t>
         </is>
       </c>
       <c r="BM445" t="inlineStr">
         <is>
-          <t>IDP</t>
-        </is>
-      </c>
-      <c r="BN445" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
+          <t>Acolhedora</t>
         </is>
       </c>
       <c r="BO445" t="inlineStr">
         <is>
-          <t>PRJ_0518</t>
+          <t>PRJ_0398</t>
         </is>
       </c>
     </row>
@@ -86405,7 +86401,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>RODE JOAO FIEL</t>
+          <t>RAIMUNDO JOSE CARLOS ASSANE</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -86420,7 +86416,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -86435,12 +86431,12 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>Cédula Pessoal</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>020107845026J</t>
+          <t>799037</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
@@ -86454,10 +86450,10 @@
         </is>
       </c>
       <c r="L446">
-        <v>1998</v>
+        <v>2007</v>
       </c>
       <c r="M446">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="N446" t="inlineStr">
         <is>
@@ -86466,7 +86462,7 @@
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t>12a classe</t>
+          <t>7a classe</t>
         </is>
       </c>
       <c r="P446" t="inlineStr">
@@ -86476,17 +86472,17 @@
       </c>
       <c r="T446" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="U446" t="inlineStr">
         <is>
-          <t>MOCIMBOA DA PRAIA</t>
+          <t>MUIDUMBI</t>
         </is>
       </c>
       <c r="V446" t="inlineStr">
         <is>
-          <t>Familia acolhedora</t>
+          <t>Sozinha/o com seu AF da sua origem</t>
         </is>
       </c>
       <c r="W446" t="inlineStr">
@@ -86521,7 +86517,7 @@
       </c>
       <c r="AF446" t="inlineStr">
         <is>
-          <t>PRODUTOS ALIMENTARES E DOMESTICOS</t>
+          <t>RECEBI KIT DOMESTICOS (BALDES, PRATOS, MANTAS)</t>
         </is>
       </c>
       <c r="AG446">
@@ -86549,49 +86545,11 @@
       </c>
       <c r="AP446" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AQ446" t="inlineStr">
-        <is>
-          <t>MATERIALBDA MACHAMBA(ENXADA)</t>
-        </is>
-      </c>
-      <c r="AR446">
-        <v>1</v>
-      </c>
-      <c r="AS446" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AU446" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AW446" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AY446" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BA446" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BB446" t="inlineStr">
-        <is>
-          <t>869-897-438</t>
-        </is>
-      </c>
-      <c r="BC446" t="inlineStr">
-        <is>
           <t>Não</t>
         </is>
       </c>
@@ -86607,17 +86565,27 @@
       </c>
       <c r="BG446" t="inlineStr">
         <is>
-          <t>871-314-984</t>
+          <t>876-314-127</t>
         </is>
       </c>
       <c r="BH446" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BI446" t="inlineStr">
+        <is>
+          <t>Mãe/pai</t>
+        </is>
+      </c>
+      <c r="BJ446" t="inlineStr">
+        <is>
+          <t>872-498-991</t>
         </is>
       </c>
       <c r="BK446" t="inlineStr">
         <is>
-          <t>Número proprio</t>
+          <t>Número alternativo</t>
         </is>
       </c>
       <c r="BL446" t="inlineStr">
@@ -86630,9 +86598,14 @@
           <t>IDP</t>
         </is>
       </c>
+      <c r="BN446" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
       <c r="BO446" t="inlineStr">
         <is>
-          <t>PRJ_0522</t>
+          <t>PRJ_0518</t>
         </is>
       </c>
     </row>
@@ -86644,7 +86617,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>SAVIANA JORGE AMADO</t>
+          <t>RODE JOAO FIEL</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -86659,7 +86632,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -86674,12 +86647,12 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Cédula Pessoal</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>020108070877J</t>
+          <t>020107845026J</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
@@ -86689,14 +86662,14 @@
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>Feminino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="L447">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="M447">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="N447" t="inlineStr">
         <is>
@@ -86710,60 +86683,42 @@
       </c>
       <c r="P447" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q447">
-        <v>2</v>
-      </c>
-      <c r="R447" t="inlineStr">
-        <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T447" t="inlineStr">
         <is>
-          <t>04/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="U447" t="inlineStr">
         <is>
-          <t>MUIDUMBI</t>
+          <t>MOCIMBOA DA PRAIA</t>
         </is>
       </c>
       <c r="V447" t="inlineStr">
         <is>
-          <t>Sozinha/o com seu AF da sua origem</t>
+          <t>Familia acolhedora</t>
         </is>
       </c>
       <c r="W447" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="X447" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Y447" t="inlineStr">
-        <is>
-          <t>VENDA DE BOLINHOS E BADJIA</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="Z447" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AA447" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AB447" t="inlineStr">
-        <is>
-          <t>ELECTRICIDADE INSTALADORA NO AGIR MOCAMBIQUE.</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AC447" t="inlineStr">
@@ -86778,7 +86733,7 @@
       </c>
       <c r="AF447" t="inlineStr">
         <is>
-          <t>RECEBI PRODUTOS ALIMENTARES.</t>
+          <t>PRODUTOS ALIMENTARES E DOMESTICOS</t>
         </is>
       </c>
       <c r="AG447">
@@ -86806,7 +86761,35 @@
       </c>
       <c r="AP447" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AQ447" t="inlineStr">
+        <is>
+          <t>MATERIALBDA MACHAMBA(ENXADA)</t>
+        </is>
+      </c>
+      <c r="AR447">
+        <v>1</v>
+      </c>
+      <c r="AS447" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AU447" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AW447" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AY447" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="BA447" t="inlineStr">
@@ -86816,17 +86799,12 @@
       </c>
       <c r="BB447" t="inlineStr">
         <is>
-          <t>866-159-704</t>
+          <t>869-897-438</t>
         </is>
       </c>
       <c r="BC447" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BD447" t="inlineStr">
-        <is>
-          <t>853-445-534</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BE447" t="inlineStr">
@@ -86841,7 +86819,7 @@
       </c>
       <c r="BG447" t="inlineStr">
         <is>
-          <t>867-803-973</t>
+          <t>871-314-984</t>
         </is>
       </c>
       <c r="BH447" t="inlineStr">
@@ -86866,7 +86844,7 @@
       </c>
       <c r="BO447" t="inlineStr">
         <is>
-          <t>PRJ_0500</t>
+          <t>PRJ_0522</t>
         </is>
       </c>
     </row>
@@ -86878,7 +86856,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>SUALEHE RAFAEL</t>
+          <t>SAVIANA JORGE AMADO</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -86893,7 +86871,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -86908,12 +86886,12 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>Cartão de Eleitor</t>
+          <t>Cédula Pessoal</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>092117-25042355868</t>
+          <t>020108070877J</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
@@ -86923,23 +86901,23 @@
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Feminino</t>
         </is>
       </c>
       <c r="L448">
-        <v>1998</v>
+        <v>2002</v>
       </c>
       <c r="M448">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t>Casada/o</t>
+          <t>Solteria/o</t>
         </is>
       </c>
       <c r="O448" t="inlineStr">
         <is>
-          <t>7a classe</t>
+          <t>12a classe</t>
         </is>
       </c>
       <c r="P448" t="inlineStr">
@@ -86948,13 +86926,33 @@
         </is>
       </c>
       <c r="Q448">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R448" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>04/2020</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>MUIDUMBI</t>
+        </is>
+      </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>Sozinha/o com seu AF da sua origem</t>
+        </is>
+      </c>
+      <c r="W448" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="X448" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -86962,17 +86960,22 @@
       </c>
       <c r="Y448" t="inlineStr">
         <is>
-          <t>CORTE E COSTURA</t>
+          <t>VENDA DE BOLINHOS E BADJIA</t>
         </is>
       </c>
       <c r="Z448" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="AA448" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AB448" t="inlineStr">
+        <is>
+          <t>ELECTRICIDADE INSTALADORA NO AGIR MOCAMBIQUE.</t>
         </is>
       </c>
       <c r="AC448" t="inlineStr">
@@ -86987,7 +86990,7 @@
       </c>
       <c r="AF448" t="inlineStr">
         <is>
-          <t>RECEBI MATERIAL DOMESTISCO (PANELAS, BALDE)</t>
+          <t>RECEBI PRODUTOS ALIMENTARES.</t>
         </is>
       </c>
       <c r="AG448">
@@ -87015,35 +87018,7 @@
       </c>
       <c r="AP448" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AQ448" t="inlineStr">
-        <is>
-          <t>RECEBI MATERIAL PARA MACHAMBA (ENCHADAS E PA)</t>
-        </is>
-      </c>
-      <c r="AR448">
-        <v>1</v>
-      </c>
-      <c r="AS448" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AU448" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AW448" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
-        </is>
-      </c>
-      <c r="AY448" t="inlineStr">
-        <is>
-          <t>##N/A##</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="BA448" t="inlineStr">
@@ -87053,12 +87028,17 @@
       </c>
       <c r="BB448" t="inlineStr">
         <is>
-          <t>873-465-513</t>
+          <t>866-159-704</t>
         </is>
       </c>
       <c r="BC448" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BD448" t="inlineStr">
+        <is>
+          <t>853-445-534</t>
         </is>
       </c>
       <c r="BE448" t="inlineStr">
@@ -87068,12 +87048,12 @@
       </c>
       <c r="BF448" t="inlineStr">
         <is>
-          <t>Esposo/a</t>
+          <t>Mãe/pai</t>
         </is>
       </c>
       <c r="BG448" t="inlineStr">
         <is>
-          <t>865-479-466</t>
+          <t>867-803-973</t>
         </is>
       </c>
       <c r="BH448" t="inlineStr">
@@ -87088,17 +87068,17 @@
       </c>
       <c r="BL448" t="inlineStr">
         <is>
-          <t>Familia acolhedora</t>
+          <t>Deslocado</t>
         </is>
       </c>
       <c r="BM448" t="inlineStr">
         <is>
-          <t>Acolhedora</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="BO448" t="inlineStr">
         <is>
-          <t>PRJ_0373</t>
+          <t>PRJ_0500</t>
         </is>
       </c>
     </row>
@@ -87110,7 +87090,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>ZITO RUFINO ALBERTO  JOAO</t>
+          <t>SUALEHE RAFAEL</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -87125,7 +87105,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Paulo Alexandre &amp; Tomas Augusto</t>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -87140,12 +87120,12 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>Cartão de Eleitor</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>031308875037M</t>
+          <t>092117-25042355868</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
@@ -87159,29 +87139,42 @@
         </is>
       </c>
       <c r="L449">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="M449">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="N449" t="inlineStr">
         <is>
-          <t>Solteria/o</t>
+          <t>Casada/o</t>
         </is>
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t>12a classe</t>
+          <t>7a classe</t>
         </is>
       </c>
       <c r="P449" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q449">
+        <v>1</v>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
       <c r="X449" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Y449" t="inlineStr">
+        <is>
+          <t>CORTE E COSTURA</t>
         </is>
       </c>
       <c r="Z449" t="inlineStr">
@@ -87206,7 +87199,7 @@
       </c>
       <c r="AF449" t="inlineStr">
         <is>
-          <t>PRODUTOS ALIMENTARES</t>
+          <t>RECEBI MATERIAL DOMESTISCO (PANELAS, BALDE)</t>
         </is>
       </c>
       <c r="AG449">
@@ -87234,7 +87227,35 @@
       </c>
       <c r="AP449" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AQ449" t="inlineStr">
+        <is>
+          <t>RECEBI MATERIAL PARA MACHAMBA (ENCHADAS E PA)</t>
+        </is>
+      </c>
+      <c r="AR449">
+        <v>1</v>
+      </c>
+      <c r="AS449" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AU449" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AW449" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AY449" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
         </is>
       </c>
       <c r="BA449" t="inlineStr">
@@ -87244,55 +87265,246 @@
       </c>
       <c r="BB449" t="inlineStr">
         <is>
+          <t>873-465-513</t>
+        </is>
+      </c>
+      <c r="BC449" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="BE449" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BF449" t="inlineStr">
+        <is>
+          <t>Esposo/a</t>
+        </is>
+      </c>
+      <c r="BG449" t="inlineStr">
+        <is>
+          <t>865-479-466</t>
+        </is>
+      </c>
+      <c r="BH449" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="BK449" t="inlineStr">
+        <is>
+          <t>Número proprio</t>
+        </is>
+      </c>
+      <c r="BL449" t="inlineStr">
+        <is>
+          <t>Familia acolhedora</t>
+        </is>
+      </c>
+      <c r="BM449" t="inlineStr">
+        <is>
+          <t>Acolhedora</t>
+        </is>
+      </c>
+      <c r="BO449" t="inlineStr">
+        <is>
+          <t>PRJ_0373</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>ZITO RUFINO ALBERTO  JOAO</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Activa</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Paulo alexandre &amp; Tomas Nhampa</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Turma 7</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>031308875037M</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>VILA SEDE</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="L450">
+        <v>2002</v>
+      </c>
+      <c r="M450">
+        <v>23</v>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>Solteria/o</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>12a classe</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="X450" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="Z450" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AA450" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AC450" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AE450" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AF450" t="inlineStr">
+        <is>
+          <t>PRODUTOS ALIMENTARES</t>
+        </is>
+      </c>
+      <c r="AG450">
+        <v>1</v>
+      </c>
+      <c r="AH450" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AJ450" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AL450" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AN450" t="inlineStr">
+        <is>
+          <t>##N/A##</t>
+        </is>
+      </c>
+      <c r="AP450" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="BA450" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BB450" t="inlineStr">
+        <is>
           <t>862-654-370</t>
         </is>
       </c>
-      <c r="BC449" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="BE449" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BF449" t="inlineStr">
+      <c r="BC450" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="BE450" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BF450" t="inlineStr">
         <is>
           <t>Outro</t>
         </is>
       </c>
-      <c r="BG449" t="inlineStr">
+      <c r="BG450" t="inlineStr">
         <is>
           <t>872-498-991</t>
         </is>
       </c>
-      <c r="BH449" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="BK449" t="inlineStr">
+      <c r="BH450" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="BK450" t="inlineStr">
         <is>
           <t>Número proprio</t>
         </is>
       </c>
-      <c r="BL449" t="inlineStr">
+      <c r="BL450" t="inlineStr">
         <is>
           <t>Familia acolhedora</t>
         </is>
       </c>
-      <c r="BM449" t="inlineStr">
+      <c r="BM450" t="inlineStr">
         <is>
           <t>Acolhedora</t>
         </is>
       </c>
-      <c r="BN449" t="inlineStr">
+      <c r="BN450" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="BO449" t="inlineStr">
+      <c r="BO450" t="inlineStr">
         <is>
           <t>PRJ_0380</t>
         </is>
@@ -87559,13 +87771,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357B4E4D-8AAD-4FAF-8EFC-0A62194B25F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A365EA41-9545-4C09-82C7-BFC330C434A2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F846CC0-9C73-4B72-9F5D-E74F02ED31DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE30EE31-0471-40D8-BD54-C240E5AFA587}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40889483-A0BE-4200-86E8-4C3E9C21F653}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68BB1985-233F-4CF7-8154-D097193B06F5}"/>
 </file>